--- a/InputData/elec/PMCRS/Pol Mandated Cap Retro Sched.xlsx
+++ b/InputData/elec/PMCRS/Pol Mandated Cap Retro Sched.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\PMCRS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\eps-mexico\InputData\elec\PMCRS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F157B3B7-0A7B-42DB-A658-FA72DDDDB9B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ADD6827-57B5-4C85-8717-D6C4732E78D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{9199B2FD-BD64-4DD1-9285-C284D90C08CC}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="5" xr2:uid="{9199B2FD-BD64-4DD1-9285-C284D90C08CC}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -145,9 +145,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId7"/>
-    <pivotCache cacheId="7" r:id="rId8"/>
-    <pivotCache cacheId="8" r:id="rId9"/>
+    <pivotCache cacheId="31" r:id="rId7"/>
+    <pivotCache cacheId="32" r:id="rId8"/>
+    <pivotCache cacheId="33" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1678,7 +1678,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -2010,6 +2010,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="16">
     <cellStyle name="Body: normal cell" xfId="6" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
@@ -76181,7 +76182,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0A00-000002000000}" name="PivotTable3" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0A00-000002000000}" name="PivotTable3" cacheId="32" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A57:I76" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField axis="axisCol" showAll="0">
@@ -76338,7 +76339,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0A00-000000000000}" name="PivotTable1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0A00-000000000000}" name="PivotTable1" cacheId="33" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A5:I25" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="15">
     <pivotField axis="axisCol" showAll="0">
@@ -76533,7 +76534,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0A00-000001000000}" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0A00-000001000000}" name="PivotTable2" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A33:I52" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="15">
     <pivotField axis="axisCol" showAll="0" sortType="ascending">
@@ -77008,12 +77009,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="2" max="2" width="67.140625" customWidth="1"/>
+    <col min="2" max="2" width="67.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>283</v>
       </c>
@@ -77022,11 +77023,11 @@
       <c r="F1" s="45"/>
       <c r="G1" s="45"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.75">
       <c r="F2" s="45"/>
       <c r="G2" s="45"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -77036,215 +77037,215 @@
       <c r="F3" s="45"/>
       <c r="G3" s="45"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.75">
       <c r="B4" t="s">
         <v>278</v>
       </c>
       <c r="F4" s="45"/>
       <c r="G4" s="45"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.75">
       <c r="B5" t="s">
         <v>279</v>
       </c>
       <c r="F5" s="45"/>
       <c r="G5" s="45"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.75">
       <c r="B6" s="3">
         <v>2024</v>
       </c>
       <c r="F6" s="45"/>
       <c r="G6" s="45"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.75">
       <c r="B7" t="s">
         <v>280</v>
       </c>
       <c r="F7" s="45"/>
       <c r="G7" s="45"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.75">
       <c r="B8" t="s">
         <v>281</v>
       </c>
       <c r="F8" s="45"/>
       <c r="G8" s="45"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.75">
       <c r="F9" s="45"/>
       <c r="G9" s="45"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F10" s="45"/>
       <c r="G10" s="45"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>2</v>
       </c>
       <c r="F11" s="45"/>
       <c r="G11" s="45"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>195</v>
       </c>
       <c r="F12" s="45"/>
       <c r="G12" s="45"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>3</v>
       </c>
       <c r="F13" s="45"/>
       <c r="G13" s="45"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>4</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.75">
       <c r="F15" s="45"/>
       <c r="G15" s="45"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>284</v>
       </c>
       <c r="F16" s="45"/>
       <c r="G16" s="45"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>282</v>
       </c>
       <c r="F17" s="45"/>
       <c r="G17" s="45"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.75">
       <c r="F18" s="45"/>
       <c r="G18" s="45"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.75">
       <c r="F19" s="45"/>
       <c r="G19" s="45"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.75">
       <c r="F20" s="45"/>
       <c r="G20" s="45"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.75">
       <c r="F21" s="45"/>
       <c r="G21" s="45"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.75">
       <c r="F22" s="45"/>
       <c r="G22" s="45"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.75">
       <c r="F23" s="45"/>
       <c r="G23" s="45"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.75">
       <c r="F24" s="45"/>
       <c r="G24" s="45"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.75">
       <c r="F25" s="45"/>
       <c r="G25" s="45"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.75">
       <c r="F26" s="45"/>
       <c r="G26" s="45"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.75">
       <c r="F27" s="45"/>
       <c r="G27" s="45"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.75">
       <c r="F28" s="45"/>
       <c r="G28" s="45"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.75">
       <c r="F29" s="45"/>
       <c r="G29" s="45"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.75">
       <c r="F30" s="45"/>
       <c r="G30" s="45"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.75">
       <c r="F31" s="45"/>
       <c r="G31" s="45"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.75">
       <c r="F32" s="45"/>
       <c r="G32" s="45"/>
     </row>
-    <row r="33" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="6:7" x14ac:dyDescent="0.75">
       <c r="F33" s="45"/>
       <c r="G33" s="45"/>
     </row>
-    <row r="34" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="6:7" x14ac:dyDescent="0.75">
       <c r="F34" s="45"/>
       <c r="G34" s="45"/>
     </row>
-    <row r="35" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="6:7" x14ac:dyDescent="0.75">
       <c r="F35" s="45"/>
       <c r="G35" s="45"/>
     </row>
-    <row r="36" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="6:7" x14ac:dyDescent="0.75">
       <c r="F36" s="45"/>
       <c r="G36" s="45"/>
     </row>
-    <row r="37" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="6:7" x14ac:dyDescent="0.75">
       <c r="F37" s="45"/>
       <c r="G37" s="45"/>
     </row>
-    <row r="38" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="6:7" x14ac:dyDescent="0.75">
       <c r="F38" s="45"/>
       <c r="G38" s="45"/>
     </row>
-    <row r="39" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="6:7" x14ac:dyDescent="0.75">
       <c r="F39" s="45"/>
       <c r="G39" s="45"/>
     </row>
-    <row r="40" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="6:7" x14ac:dyDescent="0.75">
       <c r="F40" s="45"/>
       <c r="G40" s="45"/>
     </row>
-    <row r="41" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="6:7" x14ac:dyDescent="0.75">
       <c r="F41" s="45"/>
       <c r="G41" s="45"/>
     </row>
-    <row r="42" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="6:7" x14ac:dyDescent="0.75">
       <c r="F42" s="45"/>
       <c r="G42" s="45"/>
     </row>
-    <row r="43" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="6:7" x14ac:dyDescent="0.75">
       <c r="F43" s="45"/>
       <c r="G43" s="45"/>
     </row>
-    <row r="44" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="6:7" x14ac:dyDescent="0.75">
       <c r="F44" s="45"/>
       <c r="G44" s="45"/>
     </row>
-    <row r="45" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="6:7" x14ac:dyDescent="0.75">
       <c r="F45" s="45"/>
       <c r="G45" s="45"/>
     </row>
-    <row r="46" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="6:7" x14ac:dyDescent="0.75">
       <c r="F46" s="45"/>
       <c r="G46" s="45"/>
     </row>
-    <row r="47" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="6:7" x14ac:dyDescent="0.75">
       <c r="F47" s="45"/>
       <c r="G47" s="45"/>
     </row>
@@ -77257,13 +77258,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AH2837"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
+    <col min="1" max="1" width="31.86328125" customWidth="1"/>
     <col min="2" max="2" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
       <c r="B1" s="4" t="s">
         <v>44</v>
       </c>
@@ -77361,8 +77362,8 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:34" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:34" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.75"/>
+    <row r="3" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="C3" s="6" t="s">
         <v>45</v>
       </c>
@@ -77374,7 +77375,7 @@
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
     </row>
-    <row r="4" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="C4" s="6" t="s">
         <v>47</v>
       </c>
@@ -77388,7 +77389,7 @@
       </c>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="C5" s="6" t="s">
         <v>50</v>
       </c>
@@ -77400,7 +77401,7 @@
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
     </row>
-    <row r="6" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="C6" s="6" t="s">
         <v>52</v>
       </c>
@@ -77412,7 +77413,7 @@
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
     </row>
-    <row r="7" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
@@ -77420,7 +77421,7 @@
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
     </row>
-    <row r="10" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A10" s="8" t="s">
         <v>54</v>
       </c>
@@ -77431,7 +77432,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B11" s="4" t="s">
         <v>57</v>
       </c>
@@ -77439,7 +77440,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B12" s="4"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
@@ -77476,7 +77477,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:34" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:34" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
       <c r="B13" s="5" t="s">
         <v>60</v>
       </c>
@@ -77577,18 +77578,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:34" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:34" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.75"/>
+    <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B15" s="12" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B16" s="12" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:34" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:34" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A17" s="13" t="s">
         <v>64</v>
       </c>
@@ -77692,7 +77693,7 @@
         <v>-3.5593E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A18" s="8" t="s">
         <v>66</v>
       </c>
@@ -77796,7 +77797,7 @@
         <v>-1.1639E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A19" s="8" t="s">
         <v>68</v>
       </c>
@@ -77900,7 +77901,7 @@
         <v>2.2079999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A20" s="8" t="s">
         <v>70</v>
       </c>
@@ -78004,7 +78005,7 @@
         <v>2.6945E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A21" s="8" t="s">
         <v>72</v>
       </c>
@@ -78108,7 +78109,7 @@
         <v>-2.7585999999999999E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A22" s="8" t="s">
         <v>74</v>
       </c>
@@ -78212,7 +78213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A23" s="8" t="s">
         <v>76</v>
       </c>
@@ -78316,7 +78317,7 @@
         <v>5.9369999999999999E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A24" s="8" t="s">
         <v>78</v>
       </c>
@@ -78420,7 +78421,7 @@
         <v>4.4720000000000003E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A25" s="8" t="s">
         <v>80</v>
       </c>
@@ -78524,7 +78525,7 @@
         <v>2.9822000000000001E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A26" s="8" t="s">
         <v>82</v>
       </c>
@@ -78628,7 +78629,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A27" s="8" t="s">
         <v>85</v>
       </c>
@@ -78732,12 +78733,12 @@
         <v>1.5070999999999999E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B28" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="29" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A29" s="8" t="s">
         <v>88</v>
       </c>
@@ -78841,7 +78842,7 @@
         <v>-1.9059999999999999E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A30" s="8" t="s">
         <v>90</v>
       </c>
@@ -78945,7 +78946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:34" ht="14.9" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A31" s="8" t="s">
         <v>92</v>
       </c>
@@ -79049,7 +79050,7 @@
         <v>-2.72E-4</v>
       </c>
     </row>
-    <row r="32" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:34" ht="14.9" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A32" s="8" t="s">
         <v>93</v>
       </c>
@@ -79153,7 +79154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:34" ht="14.9" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A33" s="8" t="s">
         <v>94</v>
       </c>
@@ -79257,7 +79258,7 @@
         <v>6.7999999999999999E-5</v>
       </c>
     </row>
-    <row r="34" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:34" ht="14.9" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A34" s="8" t="s">
         <v>95</v>
       </c>
@@ -79361,12 +79362,12 @@
         <v>-3.3E-4</v>
       </c>
     </row>
-    <row r="36" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:34" ht="14.9" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B36" s="12" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="37" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:34" ht="14.9" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A37" s="8" t="s">
         <v>97</v>
       </c>
@@ -79470,7 +79471,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="38" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:34" ht="14.9" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A38" s="8" t="s">
         <v>98</v>
       </c>
@@ -79574,7 +79575,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="39" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:34" ht="14.9" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A39" s="8" t="s">
         <v>99</v>
       </c>
@@ -79678,7 +79679,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="40" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:34" ht="14.9" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A40" s="8" t="s">
         <v>100</v>
       </c>
@@ -79782,7 +79783,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="41" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:34" ht="14.9" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A41" s="8" t="s">
         <v>101</v>
       </c>
@@ -79886,7 +79887,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="42" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:34" ht="14.9" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A42" s="8" t="s">
         <v>103</v>
       </c>
@@ -79990,7 +79991,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:34" ht="14.9" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A43" s="8" t="s">
         <v>104</v>
       </c>
@@ -80094,7 +80095,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:34" ht="14.9" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A44" s="8" t="s">
         <v>105</v>
       </c>
@@ -80198,7 +80199,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="45" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:34" ht="14.9" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A45" s="8" t="s">
         <v>106</v>
       </c>
@@ -80302,7 +80303,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="46" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:34" ht="14.9" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A46" s="8" t="s">
         <v>107</v>
       </c>
@@ -80406,7 +80407,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="47" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:34" ht="14.9" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A47" s="8" t="s">
         <v>109</v>
       </c>
@@ -80510,12 +80511,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="48" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:34" ht="14.9" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B48" s="12" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="49" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:34" ht="14.9" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A49" s="8" t="s">
         <v>111</v>
       </c>
@@ -80619,7 +80620,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="50" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A50" s="8" t="s">
         <v>112</v>
       </c>
@@ -80723,7 +80724,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="51" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A51" s="8" t="s">
         <v>113</v>
       </c>
@@ -80827,7 +80828,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="52" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A52" s="8" t="s">
         <v>114</v>
       </c>
@@ -80931,7 +80932,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="53" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A53" s="8" t="s">
         <v>115</v>
       </c>
@@ -81035,7 +81036,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="54" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A54" s="8" t="s">
         <v>116</v>
       </c>
@@ -81139,7 +81140,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="55" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A55" s="8" t="s">
         <v>117</v>
       </c>
@@ -81243,7 +81244,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="56" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A56" s="8" t="s">
         <v>118</v>
       </c>
@@ -81347,7 +81348,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="57" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A57" s="8" t="s">
         <v>119</v>
       </c>
@@ -81451,7 +81452,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="58" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A58" s="8" t="s">
         <v>120</v>
       </c>
@@ -81555,7 +81556,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="59" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A59" s="8" t="s">
         <v>121</v>
       </c>
@@ -81659,7 +81660,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="60" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A60" s="8" t="s">
         <v>122</v>
       </c>
@@ -81763,12 +81764,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="62" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B62" s="12" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="63" spans="1:34" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:34" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A63" s="13" t="s">
         <v>125</v>
       </c>
@@ -81872,7 +81873,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="64" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A64" s="8" t="s">
         <v>126</v>
       </c>
@@ -81976,7 +81977,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="65" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A65" s="8" t="s">
         <v>127</v>
       </c>
@@ -82080,7 +82081,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="66" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:34" ht="14.9" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A66" s="8" t="s">
         <v>128</v>
       </c>
@@ -82184,7 +82185,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="67" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A67" s="8" t="s">
         <v>129</v>
       </c>
@@ -82288,7 +82289,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A68" s="8" t="s">
         <v>130</v>
       </c>
@@ -82392,7 +82393,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="69" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A69" s="8" t="s">
         <v>131</v>
       </c>
@@ -82496,7 +82497,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="70" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A70" s="8" t="s">
         <v>132</v>
       </c>
@@ -82600,7 +82601,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="71" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A71" s="8" t="s">
         <v>133</v>
       </c>
@@ -82704,7 +82705,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="72" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A72" s="8" t="s">
         <v>134</v>
       </c>
@@ -82808,7 +82809,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="74" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A74" s="8" t="s">
         <v>135</v>
       </c>
@@ -82912,12 +82913,12 @@
         <v>1.4742999999999999E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B76" s="12" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="77" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A77" s="8" t="s">
         <v>138</v>
       </c>
@@ -83021,7 +83022,7 @@
         <v>-1.4040000000000001E-3</v>
       </c>
     </row>
-    <row r="78" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A78" s="8" t="s">
         <v>139</v>
       </c>
@@ -83125,7 +83126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:34" ht="14.9" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A79" s="8" t="s">
         <v>141</v>
       </c>
@@ -83229,7 +83230,7 @@
         <v>2.2790999999999999E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A80" s="8" t="s">
         <v>143</v>
       </c>
@@ -83333,7 +83334,7 @@
         <v>5.0600000000000005E-4</v>
       </c>
     </row>
-    <row r="81" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:34" ht="14.9" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A81" s="8" t="s">
         <v>145</v>
       </c>
@@ -83437,7 +83438,7 @@
         <v>4.8174000000000002E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A82" s="8" t="s">
         <v>146</v>
       </c>
@@ -83541,7 +83542,7 @@
         <v>2.5270000000000002E-3</v>
       </c>
     </row>
-    <row r="83" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A83" s="8" t="s">
         <v>148</v>
       </c>
@@ -83645,7 +83646,7 @@
         <v>3.9715E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A85" s="8" t="s">
         <v>149</v>
       </c>
@@ -83749,8 +83750,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:34" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="87" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:34" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.9"/>
+    <row r="87" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B87" s="143" t="s">
         <v>151</v>
       </c>
@@ -83787,127 +83788,127 @@
       <c r="AG87" s="144"/>
       <c r="AH87" s="23"/>
     </row>
-    <row r="88" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B88" s="24" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="89" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B89" s="24" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="90" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B90" s="24" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="91" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B91" s="24" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="92" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:34" ht="14.9" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B92" s="24" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="93" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B93" s="24" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="94" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B94" s="24" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="95" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B95" s="24" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="96" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B96" s="24" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="97" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B97" s="24" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="98" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B98" s="24" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="99" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B99" s="24" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="100" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B100" s="24" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="101" spans="2:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:34" ht="14.9" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B101" s="24" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="102" spans="2:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:34" ht="14.9" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B102" s="24" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="103" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B103" s="24" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="104" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B104" s="24" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="105" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B105" s="24" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="106" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B106" s="24" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="107" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B107" s="24" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="108" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B108" s="24" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="109" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B109" s="24" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="110" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B110" s="24" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="111" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B111" s="24" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="112" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B112" s="142"/>
       <c r="C112" s="142"/>
       <c r="D112" s="142"/>
@@ -83942,7 +83943,7 @@
       <c r="AG112" s="142"/>
       <c r="AH112" s="142"/>
     </row>
-    <row r="308" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B308" s="142"/>
       <c r="C308" s="142"/>
       <c r="D308" s="142"/>
@@ -83977,7 +83978,7 @@
       <c r="AG308" s="142"/>
       <c r="AH308" s="142"/>
     </row>
-    <row r="511" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B511" s="142"/>
       <c r="C511" s="142"/>
       <c r="D511" s="142"/>
@@ -84012,7 +84013,7 @@
       <c r="AG511" s="142"/>
       <c r="AH511" s="142"/>
     </row>
-    <row r="712" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B712" s="142"/>
       <c r="C712" s="142"/>
       <c r="D712" s="142"/>
@@ -84047,7 +84048,7 @@
       <c r="AG712" s="142"/>
       <c r="AH712" s="142"/>
     </row>
-    <row r="887" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="887" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B887" s="142"/>
       <c r="C887" s="142"/>
       <c r="D887" s="142"/>
@@ -84082,7 +84083,7 @@
       <c r="AG887" s="142"/>
       <c r="AH887" s="142"/>
     </row>
-    <row r="1100" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1100" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B1100" s="142"/>
       <c r="C1100" s="142"/>
       <c r="D1100" s="142"/>
@@ -84117,7 +84118,7 @@
       <c r="AG1100" s="142"/>
       <c r="AH1100" s="142"/>
     </row>
-    <row r="1227" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1227" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B1227" s="142"/>
       <c r="C1227" s="142"/>
       <c r="D1227" s="142"/>
@@ -84152,7 +84153,7 @@
       <c r="AG1227" s="142"/>
       <c r="AH1227" s="142"/>
     </row>
-    <row r="1390" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1390" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B1390" s="142"/>
       <c r="C1390" s="142"/>
       <c r="D1390" s="142"/>
@@ -84187,7 +84188,7 @@
       <c r="AG1390" s="142"/>
       <c r="AH1390" s="142"/>
     </row>
-    <row r="1502" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1502" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B1502" s="142"/>
       <c r="C1502" s="142"/>
       <c r="D1502" s="142"/>
@@ -84222,7 +84223,7 @@
       <c r="AG1502" s="142"/>
       <c r="AH1502" s="142"/>
     </row>
-    <row r="1604" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1604" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B1604" s="142"/>
       <c r="C1604" s="142"/>
       <c r="D1604" s="142"/>
@@ -84257,7 +84258,7 @@
       <c r="AG1604" s="142"/>
       <c r="AH1604" s="142"/>
     </row>
-    <row r="1698" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1698" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B1698" s="142"/>
       <c r="C1698" s="142"/>
       <c r="D1698" s="142"/>
@@ -84292,7 +84293,7 @@
       <c r="AG1698" s="142"/>
       <c r="AH1698" s="142"/>
     </row>
-    <row r="1945" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1945" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B1945" s="142"/>
       <c r="C1945" s="142"/>
       <c r="D1945" s="142"/>
@@ -84327,7 +84328,7 @@
       <c r="AG1945" s="142"/>
       <c r="AH1945" s="142"/>
     </row>
-    <row r="2031" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2031" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B2031" s="142"/>
       <c r="C2031" s="142"/>
       <c r="D2031" s="142"/>
@@ -84362,7 +84363,7 @@
       <c r="AG2031" s="142"/>
       <c r="AH2031" s="142"/>
     </row>
-    <row r="2153" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2153" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B2153" s="142"/>
       <c r="C2153" s="142"/>
       <c r="D2153" s="142"/>
@@ -84397,7 +84398,7 @@
       <c r="AG2153" s="142"/>
       <c r="AH2153" s="142"/>
     </row>
-    <row r="2317" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2317" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B2317" s="142"/>
       <c r="C2317" s="142"/>
       <c r="D2317" s="142"/>
@@ -84432,7 +84433,7 @@
       <c r="AG2317" s="142"/>
       <c r="AH2317" s="142"/>
     </row>
-    <row r="2419" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2419" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B2419" s="142"/>
       <c r="C2419" s="142"/>
       <c r="D2419" s="142"/>
@@ -84467,7 +84468,7 @@
       <c r="AG2419" s="142"/>
       <c r="AH2419" s="142"/>
     </row>
-    <row r="2509" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2509" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B2509" s="142"/>
       <c r="C2509" s="142"/>
       <c r="D2509" s="142"/>
@@ -84502,7 +84503,7 @@
       <c r="AG2509" s="142"/>
       <c r="AH2509" s="142"/>
     </row>
-    <row r="2598" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2598" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B2598" s="142"/>
       <c r="C2598" s="142"/>
       <c r="D2598" s="142"/>
@@ -84537,7 +84538,7 @@
       <c r="AG2598" s="142"/>
       <c r="AH2598" s="142"/>
     </row>
-    <row r="2719" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2719" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B2719" s="142"/>
       <c r="C2719" s="142"/>
       <c r="D2719" s="142"/>
@@ -84572,7 +84573,7 @@
       <c r="AG2719" s="142"/>
       <c r="AH2719" s="142"/>
     </row>
-    <row r="2837" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2837" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B2837" s="142"/>
       <c r="C2837" s="142"/>
       <c r="D2837" s="142"/>
@@ -84609,6 +84610,15 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B2598:AH2598"/>
+    <mergeCell ref="B2719:AH2719"/>
+    <mergeCell ref="B2837:AH2837"/>
+    <mergeCell ref="B1945:AH1945"/>
+    <mergeCell ref="B2031:AH2031"/>
+    <mergeCell ref="B2153:AH2153"/>
+    <mergeCell ref="B2317:AH2317"/>
+    <mergeCell ref="B2419:AH2419"/>
+    <mergeCell ref="B2509:AH2509"/>
     <mergeCell ref="B1698:AH1698"/>
     <mergeCell ref="B87:AG87"/>
     <mergeCell ref="B112:AH112"/>
@@ -84621,15 +84631,6 @@
     <mergeCell ref="B1390:AH1390"/>
     <mergeCell ref="B1502:AH1502"/>
     <mergeCell ref="B1604:AH1604"/>
-    <mergeCell ref="B2598:AH2598"/>
-    <mergeCell ref="B2719:AH2719"/>
-    <mergeCell ref="B2837:AH2837"/>
-    <mergeCell ref="B1945:AH1945"/>
-    <mergeCell ref="B2031:AH2031"/>
-    <mergeCell ref="B2153:AH2153"/>
-    <mergeCell ref="B2317:AH2317"/>
-    <mergeCell ref="B2419:AH2419"/>
-    <mergeCell ref="B2509:AH2509"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
@@ -84639,13 +84640,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AH16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="2" max="2" width="47.5703125" style="38" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.54296875" style="38" customWidth="1"/>
+    <col min="8" max="8" width="10.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B1" s="12" t="s">
         <v>62</v>
       </c>
@@ -84774,12 +84775,12 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B2" s="12" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A3" s="8" t="s">
         <v>64</v>
       </c>
@@ -84912,12 +84913,12 @@
       </c>
       <c r="AH3" s="19"/>
     </row>
-    <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B5" s="12" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="6" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A6" s="8" t="s">
         <v>125</v>
       </c>
@@ -85050,7 +85051,7 @@
       </c>
       <c r="AH6" s="19"/>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.75">
       <c r="B8" s="25" t="s">
         <v>176</v>
       </c>
@@ -85177,7 +85178,7 @@
       </c>
       <c r="AH8" s="28"/>
     </row>
-    <row r="9" spans="1:34" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:34" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
       <c r="B9" s="29" t="s">
         <v>177</v>
       </c>
@@ -85303,7 +85304,7 @@
         <v>15.95382699999999</v>
       </c>
     </row>
-    <row r="10" spans="1:34" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:34" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A10" t="s">
         <v>178</v>
       </c>
@@ -85429,7 +85430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:34" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:34" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A11" t="s">
         <v>178</v>
       </c>
@@ -85471,10 +85472,10 @@
       <c r="AF11" s="37"/>
       <c r="AG11" s="37"/>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.75">
       <c r="H15" s="39"/>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.75">
       <c r="H16" s="28"/>
     </row>
   </sheetData>
@@ -85486,26 +85487,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:M77"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="38.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="6" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.7265625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5" customWidth="1"/>
-    <col min="13" max="13" width="37.28515625" customWidth="1"/>
+    <col min="13" max="13" width="37.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A1" s="43">
         <v>44197</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A2" s="2" t="s">
         <v>43</v>
       </c>
@@ -85513,7 +85514,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A3" s="2" t="s">
         <v>42</v>
       </c>
@@ -85521,12 +85522,12 @@
         <v>182</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.75">
       <c r="M4" s="41" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A5" s="2" t="s">
         <v>183</v>
       </c>
@@ -85534,7 +85535,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A6" s="2" t="s">
         <v>185</v>
       </c>
@@ -85563,7 +85564,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -85586,7 +85587,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
@@ -85612,7 +85613,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
@@ -85624,7 +85625,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A10" s="3" t="s">
         <v>16</v>
       </c>
@@ -85642,7 +85643,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -85666,7 +85667,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -85689,7 +85690,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A13" s="3" t="s">
         <v>13</v>
       </c>
@@ -85701,7 +85702,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A14" s="3" t="s">
         <v>9</v>
       </c>
@@ -85714,7 +85715,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A15" s="3" t="s">
         <v>20</v>
       </c>
@@ -85727,7 +85728,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A16" s="3" t="s">
         <v>12</v>
       </c>
@@ -85748,7 +85749,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A17" s="3" t="s">
         <v>23</v>
       </c>
@@ -85769,7 +85770,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A18" s="3" t="s">
         <v>7</v>
       </c>
@@ -85798,7 +85799,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A19" s="3" t="s">
         <v>19</v>
       </c>
@@ -85815,7 +85816,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A20" s="3" t="s">
         <v>21</v>
       </c>
@@ -85833,7 +85834,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A21" s="3" t="s">
         <v>6</v>
       </c>
@@ -85847,7 +85848,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A22" s="3" t="s">
         <v>14</v>
       </c>
@@ -85873,7 +85874,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -85886,7 +85887,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A24" s="3" t="s">
         <v>18</v>
       </c>
@@ -85899,7 +85900,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A25" s="3" t="s">
         <v>186</v>
       </c>
@@ -85928,15 +85929,15 @@
         <v>199.6</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.75">
       <c r="M28" s="42"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A29" s="43">
         <v>44562</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A30" s="2" t="s">
         <v>43</v>
       </c>
@@ -85944,7 +85945,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A31" s="2" t="s">
         <v>42</v>
       </c>
@@ -85952,12 +85953,12 @@
         <v>182</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.75">
       <c r="M32" s="41" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A33" s="2" t="s">
         <v>183</v>
       </c>
@@ -85965,7 +85966,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A34" s="2" t="s">
         <v>185</v>
       </c>
@@ -85994,7 +85995,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A35" s="3" t="s">
         <v>17</v>
       </c>
@@ -86021,7 +86022,7 @@
         <v>NA</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A36" s="3" t="s">
         <v>8</v>
       </c>
@@ -86050,7 +86051,7 @@
         <v>hydro</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A37" s="3" t="s">
         <v>15</v>
       </c>
@@ -86069,7 +86070,7 @@
         <v>geothermal</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A38" s="3" t="s">
         <v>16</v>
       </c>
@@ -86088,7 +86089,7 @@
         <v>biomass</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A39" s="3" t="s">
         <v>10</v>
       </c>
@@ -86115,7 +86116,7 @@
         <v>natural gas combined cycle</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A40" s="3" t="s">
         <v>11</v>
       </c>
@@ -86142,7 +86143,7 @@
         <v>natural gas peaker</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A41" s="3" t="s">
         <v>13</v>
       </c>
@@ -86163,7 +86164,7 @@
         <v>natural gas peaker</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A42" s="3" t="s">
         <v>9</v>
       </c>
@@ -86182,7 +86183,7 @@
         <v>natural gas steam turbine</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A43" s="3" t="s">
         <v>20</v>
       </c>
@@ -86203,7 +86204,7 @@
         <v>natural gas peaker</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A44" s="3" t="s">
         <v>12</v>
       </c>
@@ -86228,7 +86229,7 @@
         <v>nuclear</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A45" s="3" t="s">
         <v>23</v>
       </c>
@@ -86251,7 +86252,7 @@
         <v>offshore wind</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A46" s="3" t="s">
         <v>7</v>
       </c>
@@ -86280,7 +86281,7 @@
         <v>onshore wind</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A47" s="3" t="s">
         <v>19</v>
       </c>
@@ -86301,7 +86302,7 @@
         <v>natural gas peaker</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A48" s="3" t="s">
         <v>21</v>
       </c>
@@ -86322,7 +86323,7 @@
         <v>biomass</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A49" s="3" t="s">
         <v>6</v>
       </c>
@@ -86341,7 +86342,7 @@
         <v>petroleum</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A50" s="3" t="s">
         <v>14</v>
       </c>
@@ -86372,7 +86373,7 @@
         <v>solar PV</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A51" s="3" t="s">
         <v>22</v>
       </c>
@@ -86391,7 +86392,7 @@
         <v>solar thermal</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A52" s="3" t="s">
         <v>186</v>
       </c>
@@ -86421,20 +86422,20 @@
       </c>
       <c r="M52" s="41"/>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.75">
       <c r="M53" s="41"/>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A55" s="1">
         <v>2023</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.75">
       <c r="M56" s="41" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A57" s="2" t="s">
         <v>183</v>
       </c>
@@ -86442,7 +86443,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A58" s="2" t="s">
         <v>185</v>
       </c>
@@ -86471,7 +86472,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A59" s="3" t="s">
         <v>17</v>
       </c>
@@ -86498,7 +86499,7 @@
         <v>NA</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A60" s="3" t="s">
         <v>8</v>
       </c>
@@ -86525,7 +86526,7 @@
         <v>hydro</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A61" s="3" t="s">
         <v>15</v>
       </c>
@@ -86540,7 +86541,7 @@
         <v>geothermal</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A62" s="3" t="s">
         <v>16</v>
       </c>
@@ -86555,7 +86556,7 @@
         <v>biomass</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A63" s="3" t="s">
         <v>10</v>
       </c>
@@ -86579,7 +86580,7 @@
         <v>natural gas combined cycle</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A64" s="3" t="s">
         <v>11</v>
       </c>
@@ -86603,7 +86604,7 @@
         <v>natural gas peaker</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A65" s="3" t="s">
         <v>13</v>
       </c>
@@ -86621,7 +86622,7 @@
         <v>natural gas peaker</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A66" s="3" t="s">
         <v>9</v>
       </c>
@@ -86639,7 +86640,7 @@
         <v>natural gas steam turbine</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A67" s="3" t="s">
         <v>20</v>
       </c>
@@ -86651,7 +86652,7 @@
         <v>natural gas peaker</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A68" s="3" t="s">
         <v>12</v>
       </c>
@@ -86672,7 +86673,7 @@
         <v>nuclear</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A69" s="3" t="s">
         <v>23</v>
       </c>
@@ -86699,7 +86700,7 @@
         <v>offshore wind</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A70" s="3" t="s">
         <v>7</v>
       </c>
@@ -86729,7 +86730,7 @@
         <v>onshore wind</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A71" s="3" t="s">
         <v>19</v>
       </c>
@@ -86741,7 +86742,7 @@
         <v>natural gas peaker</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A72" s="3" t="s">
         <v>21</v>
       </c>
@@ -86756,7 +86757,7 @@
         <v>biomass</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A73" s="3" t="s">
         <v>6</v>
       </c>
@@ -86768,7 +86769,7 @@
         <v>petroleum</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A74" s="3" t="s">
         <v>14</v>
       </c>
@@ -86801,7 +86802,7 @@
         <v>solar PV</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A75" s="3" t="s">
         <v>22</v>
       </c>
@@ -86813,7 +86814,7 @@
         <v>solar thermal</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A76" s="3" t="s">
         <v>18</v>
       </c>
@@ -86825,7 +86826,7 @@
         <v>biomass</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.75">
       <c r="M77" s="41" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
@@ -86839,14 +86840,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2FC87D5-F70B-4E40-8A44-F4753F5E6E9B}">
   <dimension ref="A1:AG158"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="65.28515625" style="99" customWidth="1"/>
+    <col min="1" max="1" width="65.26953125" style="99" customWidth="1"/>
     <col min="2" max="2" width="2" style="99" customWidth="1"/>
-    <col min="3" max="8" width="8.42578125" style="50" customWidth="1"/>
+    <col min="3" max="8" width="8.40625" style="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A1" s="49"/>
       <c r="B1" s="49"/>
       <c r="C1" s="49"/>
@@ -86855,7 +86856,7 @@
       <c r="F1" s="49"/>
       <c r="G1"/>
     </row>
-    <row r="2" spans="1:14" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:14" ht="25.25" x14ac:dyDescent="1.05">
       <c r="A2" s="145" t="s">
         <v>196</v>
       </c>
@@ -86866,7 +86867,7 @@
       <c r="F2" s="145"/>
       <c r="G2" s="145"/>
     </row>
-    <row r="3" spans="1:14" ht="18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="18" x14ac:dyDescent="0.8">
       <c r="A3" s="49"/>
       <c r="B3" s="49"/>
       <c r="C3" s="49"/>
@@ -86879,7 +86880,7 @@
       <c r="M3" s="146"/>
       <c r="N3" s="146"/>
     </row>
-    <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.8">
       <c r="A4" s="147" t="s">
         <v>197</v>
       </c>
@@ -86890,7 +86891,7 @@
       <c r="F4" s="147"/>
       <c r="G4" s="147"/>
     </row>
-    <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.8">
       <c r="A5" s="49"/>
       <c r="B5" s="146"/>
       <c r="C5" s="146"/>
@@ -86899,7 +86900,7 @@
       <c r="F5" s="49"/>
       <c r="G5"/>
     </row>
-    <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.75">
       <c r="A6" s="51"/>
       <c r="B6" s="51"/>
       <c r="C6" s="51" t="s">
@@ -86910,7 +86911,7 @@
       <c r="F6" s="51"/>
       <c r="G6" s="51"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A7" s="148"/>
       <c r="B7" s="148"/>
       <c r="C7" s="148"/>
@@ -86919,7 +86920,7 @@
       <c r="F7" s="148"/>
       <c r="G7" s="148"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A8" s="53"/>
       <c r="B8" s="53"/>
       <c r="C8" s="53"/>
@@ -86928,7 +86929,7 @@
       <c r="F8" s="53"/>
       <c r="G8" s="53"/>
     </row>
-    <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A9" s="54" t="s">
         <v>199</v>
       </c>
@@ -86937,7 +86938,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="18.75" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A10" s="56" t="s">
         <v>201</v>
       </c>
@@ -86965,7 +86966,7 @@
       </c>
       <c r="J10" s="60"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A11" s="61" t="s">
         <v>202</v>
       </c>
@@ -86993,7 +86994,7 @@
       </c>
       <c r="J11" s="67"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A12" s="68" t="s">
         <v>203</v>
       </c>
@@ -87021,7 +87022,7 @@
       </c>
       <c r="J12" s="72"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A13" s="61" t="s">
         <v>204</v>
       </c>
@@ -87049,7 +87050,7 @@
       </c>
       <c r="J13" s="75"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A14" s="68" t="s">
         <v>205</v>
       </c>
@@ -87077,7 +87078,7 @@
       </c>
       <c r="J14" s="78"/>
     </row>
-    <row r="15" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A15" s="79" t="s">
         <v>206</v>
       </c>
@@ -87105,7 +87106,7 @@
       </c>
       <c r="J15" s="78"/>
     </row>
-    <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A16" s="62"/>
       <c r="B16" s="62"/>
       <c r="C16" s="84"/>
@@ -87115,7 +87116,7 @@
       <c r="G16" s="84"/>
       <c r="H16" s="85"/>
     </row>
-    <row r="17" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A17" s="56" t="s">
         <v>207</v>
       </c>
@@ -87143,7 +87144,7 @@
       </c>
       <c r="J17" s="60"/>
     </row>
-    <row r="18" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A18" s="86" t="s">
         <v>208</v>
       </c>
@@ -87171,7 +87172,7 @@
       </c>
       <c r="J18" s="90"/>
     </row>
-    <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A19" s="62"/>
       <c r="B19" s="62"/>
       <c r="C19" s="91"/>
@@ -87181,7 +87182,7 @@
       <c r="G19" s="91"/>
       <c r="H19" s="92"/>
     </row>
-    <row r="20" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A20" s="56" t="s">
         <v>209</v>
       </c>
@@ -87209,7 +87210,7 @@
       </c>
       <c r="J20" s="60"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A21" s="61" t="s">
         <v>210</v>
       </c>
@@ -87237,7 +87238,7 @@
       </c>
       <c r="J21" s="95"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A22" s="68" t="s">
         <v>211</v>
       </c>
@@ -87251,7 +87252,7 @@
       <c r="I22" s="97"/>
       <c r="J22" s="95"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A23" s="98" t="s">
         <v>212</v>
       </c>
@@ -87278,7 +87279,7 @@
       </c>
       <c r="J23" s="95"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A24" s="100" t="s">
         <v>213</v>
       </c>
@@ -87306,7 +87307,7 @@
       </c>
       <c r="J24" s="95"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A25" s="61" t="s">
         <v>214</v>
       </c>
@@ -87320,7 +87321,7 @@
       <c r="I25" s="94"/>
       <c r="J25" s="95"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A26" s="100" t="s">
         <v>215</v>
       </c>
@@ -87348,7 +87349,7 @@
       </c>
       <c r="J26" s="95"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A27" s="98" t="s">
         <v>216</v>
       </c>
@@ -87367,7 +87368,7 @@
       <c r="I27" s="94"/>
       <c r="J27" s="95"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A28" s="100" t="s">
         <v>217</v>
       </c>
@@ -87395,7 +87396,7 @@
       </c>
       <c r="J28" s="95"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A29" s="98" t="s">
         <v>218</v>
       </c>
@@ -87416,7 +87417,7 @@
       <c r="I29" s="94"/>
       <c r="J29" s="95"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A30" s="100" t="s">
         <v>219</v>
       </c>
@@ -87444,7 +87445,7 @@
       </c>
       <c r="J30" s="95"/>
     </row>
-    <row r="31" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A31" s="102" t="s">
         <v>220</v>
       </c>
@@ -87472,7 +87473,7 @@
       </c>
       <c r="J31" s="95"/>
     </row>
-    <row r="32" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A32" s="62"/>
       <c r="B32" s="62"/>
       <c r="C32" s="106"/>
@@ -87485,7 +87486,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="33" spans="1:33" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:33" ht="18.75" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A33" s="56" t="s">
         <v>221</v>
       </c>
@@ -87582,7 +87583,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A34" s="61" t="s">
         <v>222</v>
       </c>
@@ -87610,7 +87611,7 @@
       </c>
       <c r="J34" s="109"/>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A35" s="68" t="s">
         <v>223</v>
       </c>
@@ -87638,7 +87639,7 @@
       </c>
       <c r="J35" s="109"/>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A36" s="98" t="s">
         <v>224</v>
       </c>
@@ -87666,7 +87667,7 @@
       </c>
       <c r="J36" s="109"/>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A37" s="100" t="s">
         <v>225</v>
       </c>
@@ -87694,7 +87695,7 @@
       </c>
       <c r="J37" s="109"/>
     </row>
-    <row r="38" spans="1:33" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:33" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A38" s="98" t="s">
         <v>226</v>
       </c>
@@ -87722,7 +87723,7 @@
       </c>
       <c r="J38" s="109"/>
     </row>
-    <row r="39" spans="1:33" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:33" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A39" s="100" t="s">
         <v>227</v>
       </c>
@@ -87750,7 +87751,7 @@
       </c>
       <c r="J39" s="109"/>
     </row>
-    <row r="40" spans="1:33" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:33" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A40" s="98" t="s">
         <v>228</v>
       </c>
@@ -87778,7 +87779,7 @@
       </c>
       <c r="J40" s="109"/>
     </row>
-    <row r="41" spans="1:33" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:33" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A41" s="100" t="s">
         <v>229</v>
       </c>
@@ -87806,7 +87807,7 @@
       </c>
       <c r="J41" s="109"/>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A42" s="61" t="s">
         <v>230</v>
       </c>
@@ -87833,7 +87834,7 @@
       </c>
       <c r="J42" s="109"/>
     </row>
-    <row r="43" spans="1:33" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:33" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A43" s="100" t="s">
         <v>231</v>
       </c>
@@ -87861,7 +87862,7 @@
       </c>
       <c r="J43" s="109"/>
     </row>
-    <row r="44" spans="1:33" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:33" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A44" s="98" t="s">
         <v>232</v>
       </c>
@@ -87889,7 +87890,7 @@
       </c>
       <c r="J44" s="109"/>
     </row>
-    <row r="45" spans="1:33" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:33" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A45" s="100" t="s">
         <v>233</v>
       </c>
@@ -88009,7 +88010,7 @@
         <v>0.7420077610000001</v>
       </c>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A46" s="61" t="s">
         <v>234</v>
       </c>
@@ -88036,7 +88037,7 @@
       </c>
       <c r="J46" s="109"/>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A47" s="68" t="s">
         <v>12</v>
       </c>
@@ -88064,7 +88065,7 @@
       </c>
       <c r="J47" s="109"/>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.75">
       <c r="A48" s="61" t="s">
         <v>235</v>
       </c>
@@ -88091,7 +88092,7 @@
       </c>
       <c r="J48" s="109"/>
     </row>
-    <row r="49" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A49" s="100" t="s">
         <v>236</v>
       </c>
@@ -88119,7 +88120,7 @@
       </c>
       <c r="J49" s="109"/>
     </row>
-    <row r="50" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A50" s="98" t="s">
         <v>237</v>
       </c>
@@ -88147,7 +88148,7 @@
       </c>
       <c r="J50" s="109"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A51" s="100" t="s">
         <v>238</v>
       </c>
@@ -88175,7 +88176,7 @@
       </c>
       <c r="J51" s="109"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A52" s="61" t="s">
         <v>239</v>
       </c>
@@ -88202,7 +88203,7 @@
       </c>
       <c r="J52" s="109"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A53" s="68" t="s">
         <v>240</v>
       </c>
@@ -88230,7 +88231,7 @@
       </c>
       <c r="J53" s="109"/>
     </row>
-    <row r="54" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A54" s="117" t="s">
         <v>186</v>
       </c>
@@ -88258,7 +88259,7 @@
       </c>
       <c r="J54" s="109"/>
     </row>
-    <row r="55" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" ht="16.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A55" s="62"/>
       <c r="B55" s="62"/>
       <c r="C55" s="107"/>
@@ -88268,7 +88269,7 @@
       <c r="G55" s="107"/>
       <c r="H55" s="107"/>
     </row>
-    <row r="56" spans="1:10" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" ht="18.75" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A56" s="56" t="s">
         <v>241</v>
       </c>
@@ -88296,7 +88297,7 @@
       </c>
       <c r="J56" s="60"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A57" s="61" t="s">
         <v>222</v>
       </c>
@@ -88324,7 +88325,7 @@
       </c>
       <c r="J57" s="78"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A58" s="68" t="s">
         <v>223</v>
       </c>
@@ -88352,7 +88353,7 @@
       </c>
       <c r="J58" s="122"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A59" s="98" t="s">
         <v>224</v>
       </c>
@@ -88380,7 +88381,7 @@
       </c>
       <c r="J59" s="122"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A60" s="100" t="s">
         <v>225</v>
       </c>
@@ -88408,7 +88409,7 @@
       </c>
       <c r="J60" s="122"/>
     </row>
-    <row r="61" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A61" s="98" t="s">
         <v>226</v>
       </c>
@@ -88436,7 +88437,7 @@
       </c>
       <c r="J61" s="122"/>
     </row>
-    <row r="62" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A62" s="100" t="s">
         <v>227</v>
       </c>
@@ -88464,7 +88465,7 @@
       </c>
       <c r="J62" s="122"/>
     </row>
-    <row r="63" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A63" s="98" t="s">
         <v>228</v>
       </c>
@@ -88492,7 +88493,7 @@
       </c>
       <c r="J63" s="122"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A64" s="68" t="s">
         <v>230</v>
       </c>
@@ -88520,7 +88521,7 @@
       </c>
       <c r="J64" s="122"/>
     </row>
-    <row r="65" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A65" s="98" t="s">
         <v>231</v>
       </c>
@@ -88548,7 +88549,7 @@
       </c>
       <c r="J65" s="122"/>
     </row>
-    <row r="66" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A66" s="123" t="s">
         <v>232</v>
       </c>
@@ -88576,7 +88577,7 @@
       </c>
       <c r="J66" s="122"/>
     </row>
-    <row r="67" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A67" s="98" t="s">
         <v>233</v>
       </c>
@@ -88604,7 +88605,7 @@
       </c>
       <c r="J67" s="122"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A68" s="68" t="s">
         <v>234</v>
       </c>
@@ -88632,7 +88633,7 @@
       </c>
       <c r="J68" s="122"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A69" s="61" t="s">
         <v>12</v>
       </c>
@@ -88660,7 +88661,7 @@
       </c>
       <c r="J69" s="122"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A70" s="68" t="s">
         <v>235</v>
       </c>
@@ -88688,7 +88689,7 @@
       </c>
       <c r="J70" s="122"/>
     </row>
-    <row r="71" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A71" s="98" t="s">
         <v>236</v>
       </c>
@@ -88716,7 +88717,7 @@
       </c>
       <c r="J71" s="122"/>
     </row>
-    <row r="72" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A72" s="124" t="s">
         <v>237</v>
       </c>
@@ -88744,7 +88745,7 @@
       </c>
       <c r="J72" s="122"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A73" s="98" t="s">
         <v>238</v>
       </c>
@@ -88772,7 +88773,7 @@
       </c>
       <c r="J73" s="122"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A74" s="68" t="s">
         <v>240</v>
       </c>
@@ -88800,7 +88801,7 @@
       </c>
       <c r="J74" s="122"/>
     </row>
-    <row r="75" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A75" s="125" t="s">
         <v>186</v>
       </c>
@@ -88828,7 +88829,7 @@
       </c>
       <c r="J75" s="122"/>
     </row>
-    <row r="76" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A76" s="79"/>
       <c r="B76" s="80"/>
       <c r="C76" s="129"/>
@@ -88840,7 +88841,7 @@
       <c r="I76" s="129"/>
       <c r="J76" s="122"/>
     </row>
-    <row r="77" spans="1:10" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" ht="18.75" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A77" s="56" t="s">
         <v>242</v>
       </c>
@@ -88868,7 +88869,7 @@
       </c>
       <c r="J77" s="60"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A78" s="61" t="s">
         <v>222</v>
       </c>
@@ -88896,7 +88897,7 @@
       </c>
       <c r="J78" s="78"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A79" s="68" t="s">
         <v>223</v>
       </c>
@@ -88924,7 +88925,7 @@
       </c>
       <c r="J79" s="122"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A80" s="98" t="s">
         <v>224</v>
       </c>
@@ -88952,7 +88953,7 @@
       </c>
       <c r="J80" s="122"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A81" s="100" t="s">
         <v>225</v>
       </c>
@@ -88980,7 +88981,7 @@
       </c>
       <c r="J81" s="122"/>
     </row>
-    <row r="82" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A82" s="98" t="s">
         <v>226</v>
       </c>
@@ -89008,7 +89009,7 @@
       </c>
       <c r="J82" s="122"/>
     </row>
-    <row r="83" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A83" s="100" t="s">
         <v>227</v>
       </c>
@@ -89036,7 +89037,7 @@
       </c>
       <c r="J83" s="122"/>
     </row>
-    <row r="84" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A84" s="98" t="s">
         <v>228</v>
       </c>
@@ -89064,7 +89065,7 @@
       </c>
       <c r="J84" s="122"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A85" s="68" t="s">
         <v>230</v>
       </c>
@@ -89092,7 +89093,7 @@
       </c>
       <c r="J85" s="122"/>
     </row>
-    <row r="86" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A86" s="98" t="s">
         <v>231</v>
       </c>
@@ -89120,7 +89121,7 @@
       </c>
       <c r="J86" s="122"/>
     </row>
-    <row r="87" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A87" s="123" t="s">
         <v>232</v>
       </c>
@@ -89148,7 +89149,7 @@
       </c>
       <c r="J87" s="122"/>
     </row>
-    <row r="88" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A88" s="98" t="s">
         <v>233</v>
       </c>
@@ -89176,7 +89177,7 @@
       </c>
       <c r="J88" s="122"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A89" s="68" t="s">
         <v>234</v>
       </c>
@@ -89204,7 +89205,7 @@
       </c>
       <c r="J89" s="122"/>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A90" s="61" t="s">
         <v>12</v>
       </c>
@@ -89232,7 +89233,7 @@
       </c>
       <c r="J90" s="122"/>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A91" s="68" t="s">
         <v>235</v>
       </c>
@@ -89260,7 +89261,7 @@
       </c>
       <c r="J91" s="122"/>
     </row>
-    <row r="92" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A92" s="98" t="s">
         <v>236</v>
       </c>
@@ -89288,7 +89289,7 @@
       </c>
       <c r="J92" s="122"/>
     </row>
-    <row r="93" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A93" s="124" t="s">
         <v>237</v>
       </c>
@@ -89316,7 +89317,7 @@
       </c>
       <c r="J93" s="122"/>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A94" s="98" t="s">
         <v>238</v>
       </c>
@@ -89344,7 +89345,7 @@
       </c>
       <c r="J94" s="122"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A95" s="68" t="s">
         <v>240</v>
       </c>
@@ -89372,7 +89373,7 @@
       </c>
       <c r="J95" s="122"/>
     </row>
-    <row r="96" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A96" s="125" t="s">
         <v>186</v>
       </c>
@@ -89400,7 +89401,7 @@
       </c>
       <c r="J96" s="122"/>
     </row>
-    <row r="97" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A97" s="62"/>
       <c r="B97" s="62"/>
       <c r="C97" s="107"/>
@@ -89410,7 +89411,7 @@
       <c r="G97" s="107"/>
       <c r="H97" s="107"/>
     </row>
-    <row r="98" spans="1:10" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" ht="18.75" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A98" s="56" t="s">
         <v>243</v>
       </c>
@@ -89438,7 +89439,7 @@
       </c>
       <c r="J98" s="60"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A99" s="98" t="s">
         <v>244</v>
       </c>
@@ -89465,7 +89466,7 @@
       </c>
       <c r="J99" s="122"/>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A100" s="100" t="s">
         <v>245</v>
       </c>
@@ -89493,7 +89494,7 @@
       </c>
       <c r="J100" s="122"/>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A101" s="98" t="s">
         <v>246</v>
       </c>
@@ -89520,7 +89521,7 @@
       </c>
       <c r="J101" s="122"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A102" s="100" t="s">
         <v>247</v>
       </c>
@@ -89548,7 +89549,7 @@
       </c>
       <c r="J102" s="122"/>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A103" s="98" t="s">
         <v>248</v>
       </c>
@@ -89575,7 +89576,7 @@
       </c>
       <c r="J103" s="122"/>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A104" s="100" t="s">
         <v>249</v>
       </c>
@@ -89603,7 +89604,7 @@
       </c>
       <c r="J104" s="122"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A105" s="98" t="s">
         <v>250</v>
       </c>
@@ -89630,7 +89631,7 @@
       </c>
       <c r="J105" s="122"/>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A106" s="101" t="s">
         <v>251</v>
       </c>
@@ -89658,7 +89659,7 @@
       </c>
       <c r="J106" s="122"/>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A107" s="99" t="s">
         <v>252</v>
       </c>
@@ -89685,7 +89686,7 @@
       </c>
       <c r="J107" s="109"/>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A108" s="101" t="s">
         <v>253</v>
       </c>
@@ -89712,7 +89713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A109" s="99" t="s">
         <v>254</v>
       </c>
@@ -89739,7 +89740,7 @@
       </c>
       <c r="J109" s="60"/>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A110" s="101" t="s">
         <v>255</v>
       </c>
@@ -89767,7 +89768,7 @@
       </c>
       <c r="J110" s="109"/>
     </row>
-    <row r="111" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A111" s="99" t="s">
         <v>256</v>
       </c>
@@ -89795,7 +89796,7 @@
       </c>
       <c r="J111" s="109"/>
     </row>
-    <row r="112" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A112" s="101" t="s">
         <v>257</v>
       </c>
@@ -89823,7 +89824,7 @@
       </c>
       <c r="J112" s="109"/>
     </row>
-    <row r="113" spans="1:10" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" s="114" customFormat="1" ht="15.25" thickBot="1" x14ac:dyDescent="0.85">
       <c r="A113" s="125" t="s">
         <v>186</v>
       </c>
@@ -89851,7 +89852,7 @@
       </c>
       <c r="J113" s="109"/>
     </row>
-    <row r="114" spans="1:10" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" s="114" customFormat="1" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A114" s="99"/>
       <c r="B114" s="99"/>
       <c r="C114" s="107"/>
@@ -89863,7 +89864,7 @@
       <c r="I114"/>
       <c r="J114" s="109"/>
     </row>
-    <row r="115" spans="1:10" s="114" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" s="114" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A115" s="56" t="s">
         <v>258</v>
       </c>
@@ -89891,7 +89892,7 @@
       </c>
       <c r="J115" s="109"/>
     </row>
-    <row r="116" spans="1:10" s="114" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" s="114" customFormat="1" ht="14.5" x14ac:dyDescent="0.7">
       <c r="A116" s="61" t="s">
         <v>222</v>
       </c>
@@ -89919,7 +89920,7 @@
       </c>
       <c r="J116" s="109"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A117" s="68" t="s">
         <v>223</v>
       </c>
@@ -89947,7 +89948,7 @@
       </c>
       <c r="J117" s="133"/>
     </row>
-    <row r="118" spans="1:10" s="114" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" s="114" customFormat="1" ht="14.5" x14ac:dyDescent="0.7">
       <c r="A118" s="98" t="s">
         <v>224</v>
       </c>
@@ -89975,7 +89976,7 @@
       </c>
       <c r="J118" s="109"/>
     </row>
-    <row r="119" spans="1:10" s="114" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" s="114" customFormat="1" ht="14.5" x14ac:dyDescent="0.7">
       <c r="A119" s="100" t="s">
         <v>259</v>
       </c>
@@ -90003,7 +90004,7 @@
       </c>
       <c r="J119" s="109"/>
     </row>
-    <row r="120" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A120" s="98" t="s">
         <v>225</v>
       </c>
@@ -90031,7 +90032,7 @@
       </c>
       <c r="J120" s="109"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A121" s="100" t="s">
         <v>226</v>
       </c>
@@ -90059,7 +90060,7 @@
       </c>
       <c r="J121" s="109"/>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A122" s="98" t="s">
         <v>227</v>
       </c>
@@ -90086,7 +90087,7 @@
       </c>
       <c r="J122" s="109"/>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A123" s="100" t="s">
         <v>228</v>
       </c>
@@ -90114,7 +90115,7 @@
       </c>
       <c r="J123" s="109"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A124" s="98" t="s">
         <v>229</v>
       </c>
@@ -90141,7 +90142,7 @@
       </c>
       <c r="J124" s="109"/>
     </row>
-    <row r="125" spans="1:10" s="114" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" s="114" customFormat="1" ht="14.5" x14ac:dyDescent="0.7">
       <c r="A125" s="68" t="s">
         <v>230</v>
       </c>
@@ -90169,7 +90170,7 @@
       </c>
       <c r="J125" s="109"/>
     </row>
-    <row r="126" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
       <c r="A126" s="98" t="s">
         <v>260</v>
       </c>
@@ -90197,7 +90198,7 @@
       </c>
       <c r="J126" s="109"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A127" s="100" t="s">
         <v>232</v>
       </c>
@@ -90225,7 +90226,7 @@
       </c>
       <c r="J127" s="109"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A128" s="98" t="s">
         <v>233</v>
       </c>
@@ -90252,7 +90253,7 @@
       </c>
       <c r="J128" s="109"/>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A129" s="68" t="s">
         <v>234</v>
       </c>
@@ -90280,7 +90281,7 @@
       </c>
       <c r="J129" s="109"/>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A130" s="61" t="s">
         <v>12</v>
       </c>
@@ -90307,7 +90308,7 @@
       </c>
       <c r="J130" s="109"/>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A131" s="68" t="s">
         <v>235</v>
       </c>
@@ -90335,7 +90336,7 @@
       </c>
       <c r="J131" s="109"/>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A132" s="98" t="s">
         <v>236</v>
       </c>
@@ -90361,7 +90362,7 @@
         <v>1060.4055484272631</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A133" s="100" t="s">
         <v>237</v>
       </c>
@@ -90389,7 +90390,7 @@
       </c>
       <c r="J133" s="60"/>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A134" s="98" t="s">
         <v>238</v>
       </c>
@@ -90416,7 +90417,7 @@
       </c>
       <c r="J134" s="109"/>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A135" s="68" t="s">
         <v>239</v>
       </c>
@@ -90444,7 +90445,7 @@
       </c>
       <c r="J135" s="109"/>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A136" s="61" t="s">
         <v>240</v>
       </c>
@@ -90471,7 +90472,7 @@
       </c>
       <c r="J136" s="109"/>
     </row>
-    <row r="137" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A137" s="134" t="s">
         <v>186</v>
       </c>
@@ -90499,7 +90500,7 @@
       </c>
       <c r="J137" s="109"/>
     </row>
-    <row r="138" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10" ht="16.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A138" s="62"/>
       <c r="B138" s="62"/>
       <c r="C138" s="107"/>
@@ -90510,7 +90511,7 @@
       <c r="H138" s="107"/>
       <c r="J138" s="109"/>
     </row>
-    <row r="139" spans="1:10" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" ht="18.75" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A139" s="56" t="s">
         <v>261</v>
       </c>
@@ -90538,7 +90539,7 @@
       </c>
       <c r="J139" s="109"/>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A140" s="61" t="s">
         <v>262</v>
       </c>
@@ -90566,7 +90567,7 @@
       </c>
       <c r="J140" s="109"/>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A141" s="100" t="s">
         <v>263</v>
       </c>
@@ -90580,7 +90581,7 @@
       <c r="I141" s="111"/>
       <c r="J141" s="109"/>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A142" s="98" t="s">
         <v>264</v>
       </c>
@@ -90601,7 +90602,7 @@
       <c r="I142" s="108"/>
       <c r="J142" s="109"/>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A143" s="100" t="s">
         <v>265</v>
       </c>
@@ -90621,7 +90622,7 @@
       <c r="I143" s="111"/>
       <c r="J143" s="109"/>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A144" s="98" t="s">
         <v>266</v>
       </c>
@@ -90648,7 +90649,7 @@
       </c>
       <c r="J144" s="109"/>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A145" s="100" t="s">
         <v>267</v>
       </c>
@@ -90670,7 +90671,7 @@
       <c r="I145" s="111"/>
       <c r="J145" s="109"/>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A146" s="98" t="s">
         <v>268</v>
       </c>
@@ -90697,7 +90698,7 @@
       </c>
       <c r="J146" s="109"/>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A147" s="100" t="s">
         <v>269</v>
       </c>
@@ -90725,7 +90726,7 @@
       </c>
       <c r="J147" s="109"/>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A148" s="98" t="s">
         <v>264</v>
       </c>
@@ -90752,7 +90753,7 @@
       </c>
       <c r="J148" s="109"/>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A149" s="100" t="s">
         <v>266</v>
       </c>
@@ -90780,7 +90781,7 @@
       </c>
       <c r="J149" s="75"/>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A150" s="98" t="s">
         <v>268</v>
       </c>
@@ -90806,7 +90807,7 @@
         <v>39.010000009234588</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A151" s="68" t="s">
         <v>270</v>
       </c>
@@ -90833,7 +90834,7 @@
         <v>5.2116030849019062</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A152" s="98" t="s">
         <v>271</v>
       </c>
@@ -90853,7 +90854,7 @@
       <c r="H152" s="107"/>
       <c r="I152" s="108"/>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A153" s="100" t="s">
         <v>272</v>
       </c>
@@ -90880,7 +90881,7 @@
         <v>2.5205571355626204</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A154" s="98" t="s">
         <v>273</v>
       </c>
@@ -90906,7 +90907,7 @@
         <v>2.6910459493392862</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A155" s="100"/>
       <c r="B155" s="101"/>
       <c r="C155" s="110"/>
@@ -90917,7 +90918,7 @@
       <c r="H155" s="110"/>
       <c r="I155" s="111"/>
     </row>
-    <row r="156" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:10" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A156" s="79" t="s">
         <v>274</v>
       </c>
@@ -90944,7 +90945,7 @@
         <v>7.8382324901165461</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.75">
       <c r="C157" s="73"/>
       <c r="D157" s="73"/>
       <c r="E157" s="73"/>
@@ -90953,7 +90954,7 @@
       <c r="H157" s="73"/>
       <c r="I157" s="73"/>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A158" s="99" t="s">
         <v>275</v>
       </c>
@@ -90978,20 +90979,20 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AF25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AZ25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="27" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="32" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.26953125" customWidth="1"/>
+    <col min="7" max="7" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="18" max="27" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="29" max="32" width="10.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>194</v>
       </c>
@@ -91088,2356 +91089,3856 @@
       <c r="AF1">
         <v>2050</v>
       </c>
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A2" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="47">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47">
-        <v>0</v>
-      </c>
-      <c r="D2" s="47">
-        <v>0</v>
-      </c>
-      <c r="E2" s="47">
-        <v>0</v>
-      </c>
-      <c r="F2" s="47">
-        <v>0</v>
-      </c>
-      <c r="G2" s="47">
-        <v>0</v>
-      </c>
-      <c r="H2" s="47">
-        <v>0</v>
-      </c>
-      <c r="I2" s="47">
-        <v>0</v>
-      </c>
-      <c r="J2" s="47">
-        <v>0</v>
-      </c>
-      <c r="K2" s="47">
-        <v>0</v>
-      </c>
-      <c r="L2" s="47">
-        <v>0</v>
-      </c>
-      <c r="M2" s="47">
-        <v>0</v>
-      </c>
-      <c r="N2" s="47">
-        <v>0</v>
-      </c>
-      <c r="O2" s="47">
-        <v>0</v>
-      </c>
-      <c r="P2" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="47">
-        <v>0</v>
-      </c>
-      <c r="R2" s="47">
-        <v>0</v>
-      </c>
-      <c r="S2" s="47">
-        <v>0</v>
-      </c>
-      <c r="T2" s="47">
-        <v>0</v>
-      </c>
-      <c r="U2" s="47">
-        <v>0</v>
-      </c>
-      <c r="V2" s="47">
-        <v>0</v>
-      </c>
-      <c r="W2" s="47">
-        <v>0</v>
-      </c>
-      <c r="X2" s="47">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="47">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="47">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="47">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="47">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="47">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="47">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="47">
-        <v>0</v>
-      </c>
-      <c r="AF2" s="47">
+      <c r="B2" s="149">
+        <v>0</v>
+      </c>
+      <c r="C2" s="149">
+        <v>0</v>
+      </c>
+      <c r="D2" s="149">
+        <v>0</v>
+      </c>
+      <c r="E2" s="149">
+        <v>0</v>
+      </c>
+      <c r="F2" s="149">
+        <v>0</v>
+      </c>
+      <c r="G2" s="149">
+        <v>0</v>
+      </c>
+      <c r="H2" s="149">
+        <v>0</v>
+      </c>
+      <c r="I2" s="149">
+        <v>0</v>
+      </c>
+      <c r="J2" s="149">
+        <v>0</v>
+      </c>
+      <c r="K2" s="149">
+        <v>0</v>
+      </c>
+      <c r="L2" s="149">
+        <v>0</v>
+      </c>
+      <c r="M2" s="149">
+        <v>0</v>
+      </c>
+      <c r="N2" s="149">
+        <v>0</v>
+      </c>
+      <c r="O2" s="149">
+        <v>0</v>
+      </c>
+      <c r="P2" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="149">
+        <v>0</v>
+      </c>
+      <c r="R2" s="149">
+        <v>0</v>
+      </c>
+      <c r="S2" s="149">
+        <v>0</v>
+      </c>
+      <c r="T2" s="149">
+        <v>0</v>
+      </c>
+      <c r="U2" s="149">
+        <v>0</v>
+      </c>
+      <c r="V2" s="149">
+        <v>0</v>
+      </c>
+      <c r="W2" s="149">
+        <v>0</v>
+      </c>
+      <c r="X2" s="149">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="149">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="149">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="149">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="149">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="149">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="149">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="149">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="149">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="149">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="149">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="149">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="149">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="149">
+        <v>0</v>
+      </c>
+      <c r="AL2" s="149">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="149">
+        <v>0</v>
+      </c>
+      <c r="AN2" s="149">
+        <v>0</v>
+      </c>
+      <c r="AO2" s="149">
+        <v>0</v>
+      </c>
+      <c r="AP2" s="149">
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="149">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="149">
+        <v>0</v>
+      </c>
+      <c r="AS2" s="149">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="149">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="149">
+        <v>0</v>
+      </c>
+      <c r="AV2" s="149">
+        <v>0</v>
+      </c>
+      <c r="AW2" s="149">
+        <v>0</v>
+      </c>
+      <c r="AX2" s="149">
+        <v>0</v>
+      </c>
+      <c r="AY2" s="149">
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="149">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A3" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="47">
-        <v>0</v>
-      </c>
-      <c r="C3" s="47">
-        <v>0</v>
-      </c>
-      <c r="D3" s="47">
-        <v>0</v>
-      </c>
-      <c r="E3" s="47">
-        <v>0</v>
-      </c>
-      <c r="F3" s="47">
-        <v>0</v>
-      </c>
-      <c r="G3" s="47">
-        <v>0</v>
-      </c>
-      <c r="H3" s="47">
-        <v>0</v>
-      </c>
-      <c r="I3" s="47">
-        <v>0</v>
-      </c>
-      <c r="J3" s="47">
-        <v>0</v>
-      </c>
-      <c r="K3" s="47">
-        <v>0</v>
-      </c>
-      <c r="L3" s="47">
-        <v>0</v>
-      </c>
-      <c r="M3" s="47">
-        <v>0</v>
-      </c>
-      <c r="N3" s="47">
-        <v>0</v>
-      </c>
-      <c r="O3" s="47">
-        <v>0</v>
-      </c>
-      <c r="P3" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="47">
-        <v>0</v>
-      </c>
-      <c r="R3" s="47">
-        <v>0</v>
-      </c>
-      <c r="S3" s="47">
-        <v>0</v>
-      </c>
-      <c r="T3" s="47">
-        <v>0</v>
-      </c>
-      <c r="U3" s="47">
-        <v>0</v>
-      </c>
-      <c r="V3" s="47">
-        <v>0</v>
-      </c>
-      <c r="W3" s="47">
-        <v>0</v>
-      </c>
-      <c r="X3" s="47">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="47">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="47">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="47">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="47">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="47">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="47">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="47">
-        <v>0</v>
-      </c>
-      <c r="AF3" s="47">
+      <c r="B3" s="149">
+        <v>0</v>
+      </c>
+      <c r="C3" s="149">
+        <v>0</v>
+      </c>
+      <c r="D3" s="149">
+        <v>0</v>
+      </c>
+      <c r="E3" s="149">
+        <v>0</v>
+      </c>
+      <c r="F3" s="149">
+        <v>0</v>
+      </c>
+      <c r="G3" s="149">
+        <v>0</v>
+      </c>
+      <c r="H3" s="149">
+        <v>0</v>
+      </c>
+      <c r="I3" s="149">
+        <v>0</v>
+      </c>
+      <c r="J3" s="149">
+        <v>0</v>
+      </c>
+      <c r="K3" s="149">
+        <v>0</v>
+      </c>
+      <c r="L3" s="149">
+        <v>0</v>
+      </c>
+      <c r="M3" s="149">
+        <v>0</v>
+      </c>
+      <c r="N3" s="149">
+        <v>0</v>
+      </c>
+      <c r="O3" s="149">
+        <v>0</v>
+      </c>
+      <c r="P3" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="149">
+        <v>0</v>
+      </c>
+      <c r="R3" s="149">
+        <v>0</v>
+      </c>
+      <c r="S3" s="149">
+        <v>0</v>
+      </c>
+      <c r="T3" s="149">
+        <v>0</v>
+      </c>
+      <c r="U3" s="149">
+        <v>0</v>
+      </c>
+      <c r="V3" s="149">
+        <v>0</v>
+      </c>
+      <c r="W3" s="149">
+        <v>0</v>
+      </c>
+      <c r="X3" s="149">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="149">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="149">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="149">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="149">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="149">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="149">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="149">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="149">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="149">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="149">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="149">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="149">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="149">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="149">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="149">
+        <v>0</v>
+      </c>
+      <c r="AN3" s="149">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="149">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="149">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="149">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="149">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="149">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="149">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="149">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="149">
+        <v>0</v>
+      </c>
+      <c r="AW3" s="149">
+        <v>0</v>
+      </c>
+      <c r="AX3" s="149">
+        <v>0</v>
+      </c>
+      <c r="AY3" s="149">
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="149">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A4" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="47">
-        <v>0</v>
-      </c>
-      <c r="C4" s="47">
-        <v>0</v>
-      </c>
-      <c r="D4" s="47">
-        <v>0</v>
-      </c>
-      <c r="E4" s="47">
-        <v>0</v>
-      </c>
-      <c r="F4" s="47">
-        <v>0</v>
-      </c>
-      <c r="G4" s="47">
-        <v>0</v>
-      </c>
-      <c r="H4" s="47">
-        <v>0</v>
-      </c>
-      <c r="I4" s="47">
-        <v>0</v>
-      </c>
-      <c r="J4" s="47">
-        <v>0</v>
-      </c>
-      <c r="K4" s="47">
-        <v>0</v>
-      </c>
-      <c r="L4" s="47">
-        <v>0</v>
-      </c>
-      <c r="M4" s="47">
-        <v>0</v>
-      </c>
-      <c r="N4" s="47">
-        <v>0</v>
-      </c>
-      <c r="O4" s="47">
-        <v>0</v>
-      </c>
-      <c r="P4" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="47">
-        <v>0</v>
-      </c>
-      <c r="R4" s="47">
-        <v>0</v>
-      </c>
-      <c r="S4" s="47">
-        <v>0</v>
-      </c>
-      <c r="T4" s="47">
-        <v>0</v>
-      </c>
-      <c r="U4" s="47">
-        <v>0</v>
-      </c>
-      <c r="V4" s="47">
-        <v>0</v>
-      </c>
-      <c r="W4" s="47">
-        <v>0</v>
-      </c>
-      <c r="X4" s="47">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="47">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="47">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="47">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="47">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="47">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="47">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="47">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="47">
+      <c r="B4" s="149">
+        <v>0</v>
+      </c>
+      <c r="C4" s="149">
+        <v>0</v>
+      </c>
+      <c r="D4" s="149">
+        <v>0</v>
+      </c>
+      <c r="E4" s="149">
+        <v>0</v>
+      </c>
+      <c r="F4" s="149">
+        <v>0</v>
+      </c>
+      <c r="G4" s="149">
+        <v>0</v>
+      </c>
+      <c r="H4" s="149">
+        <v>0</v>
+      </c>
+      <c r="I4" s="149">
+        <v>0</v>
+      </c>
+      <c r="J4" s="149">
+        <v>0</v>
+      </c>
+      <c r="K4" s="149">
+        <v>0</v>
+      </c>
+      <c r="L4" s="149">
+        <v>0</v>
+      </c>
+      <c r="M4" s="149">
+        <v>0</v>
+      </c>
+      <c r="N4" s="149">
+        <v>0</v>
+      </c>
+      <c r="O4" s="149">
+        <v>0</v>
+      </c>
+      <c r="P4" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="149">
+        <v>0</v>
+      </c>
+      <c r="R4" s="149">
+        <v>0</v>
+      </c>
+      <c r="S4" s="149">
+        <v>0</v>
+      </c>
+      <c r="T4" s="149">
+        <v>0</v>
+      </c>
+      <c r="U4" s="149">
+        <v>0</v>
+      </c>
+      <c r="V4" s="149">
+        <v>0</v>
+      </c>
+      <c r="W4" s="149">
+        <v>0</v>
+      </c>
+      <c r="X4" s="149">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="149">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="149">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="149">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="149">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="149">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="149">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="149">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="149">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="149">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="149">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="149">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="149">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="149">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="149">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="149">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="149">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="149">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="149">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="149">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="149">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="149">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="149">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="149">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="149">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="149">
+        <v>0</v>
+      </c>
+      <c r="AX4" s="149">
+        <v>0</v>
+      </c>
+      <c r="AY4" s="149">
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="149">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A5" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="47">
-        <v>0</v>
-      </c>
-      <c r="C5" s="47">
-        <v>0</v>
-      </c>
-      <c r="D5" s="47">
-        <v>0</v>
-      </c>
-      <c r="E5" s="47">
-        <v>0</v>
-      </c>
-      <c r="F5" s="47">
-        <v>0</v>
-      </c>
-      <c r="G5" s="47">
-        <v>0</v>
-      </c>
-      <c r="H5" s="47">
-        <v>0</v>
-      </c>
-      <c r="I5" s="47">
-        <v>0</v>
-      </c>
-      <c r="J5" s="47">
-        <v>0</v>
-      </c>
-      <c r="K5" s="47">
-        <v>0</v>
-      </c>
-      <c r="L5" s="47">
-        <v>0</v>
-      </c>
-      <c r="M5" s="47">
-        <v>0</v>
-      </c>
-      <c r="N5" s="47">
-        <v>0</v>
-      </c>
-      <c r="O5" s="47">
-        <v>0</v>
-      </c>
-      <c r="P5" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="47">
-        <v>0</v>
-      </c>
-      <c r="R5" s="47">
-        <v>0</v>
-      </c>
-      <c r="S5" s="47">
-        <v>0</v>
-      </c>
-      <c r="T5" s="47">
-        <v>0</v>
-      </c>
-      <c r="U5" s="47">
-        <v>0</v>
-      </c>
-      <c r="V5" s="47">
-        <v>0</v>
-      </c>
-      <c r="W5" s="47">
-        <v>0</v>
-      </c>
-      <c r="X5" s="47">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="47">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="47">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="47">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="47">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="47">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="47">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="47">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="47">
+      <c r="B5" s="149">
+        <v>0</v>
+      </c>
+      <c r="C5" s="149">
+        <v>0</v>
+      </c>
+      <c r="D5" s="149">
+        <v>0</v>
+      </c>
+      <c r="E5" s="149">
+        <v>0</v>
+      </c>
+      <c r="F5" s="149">
+        <v>0</v>
+      </c>
+      <c r="G5" s="149">
+        <v>0</v>
+      </c>
+      <c r="H5" s="149">
+        <v>0</v>
+      </c>
+      <c r="I5" s="149">
+        <v>0</v>
+      </c>
+      <c r="J5" s="149">
+        <v>0</v>
+      </c>
+      <c r="K5" s="149">
+        <v>0</v>
+      </c>
+      <c r="L5" s="149">
+        <v>0</v>
+      </c>
+      <c r="M5" s="149">
+        <v>0</v>
+      </c>
+      <c r="N5" s="149">
+        <v>0</v>
+      </c>
+      <c r="O5" s="149">
+        <v>0</v>
+      </c>
+      <c r="P5" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="149">
+        <v>0</v>
+      </c>
+      <c r="R5" s="149">
+        <v>0</v>
+      </c>
+      <c r="S5" s="149">
+        <v>0</v>
+      </c>
+      <c r="T5" s="149">
+        <v>0</v>
+      </c>
+      <c r="U5" s="149">
+        <v>0</v>
+      </c>
+      <c r="V5" s="149">
+        <v>0</v>
+      </c>
+      <c r="W5" s="149">
+        <v>0</v>
+      </c>
+      <c r="X5" s="149">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="149">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="149">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="149">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="149">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="149">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="149">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="149">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="149">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="149">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="149">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="149">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="149">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="149">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="149">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="149">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="149">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="149">
+        <v>0</v>
+      </c>
+      <c r="AP5" s="149">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="149">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="149">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="149">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="149">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="149">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="149">
+        <v>0</v>
+      </c>
+      <c r="AW5" s="149">
+        <v>0</v>
+      </c>
+      <c r="AX5" s="149">
+        <v>0</v>
+      </c>
+      <c r="AY5" s="149">
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="149">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A6" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="47">
-        <v>0</v>
-      </c>
-      <c r="C6" s="47">
-        <v>0</v>
-      </c>
-      <c r="D6" s="47">
-        <v>0</v>
-      </c>
-      <c r="E6" s="47">
-        <v>0</v>
-      </c>
-      <c r="F6" s="47">
-        <v>0</v>
-      </c>
-      <c r="G6" s="47">
-        <v>0</v>
-      </c>
-      <c r="H6" s="47">
-        <v>0</v>
-      </c>
-      <c r="I6" s="47">
-        <v>0</v>
-      </c>
-      <c r="J6" s="47">
-        <v>0</v>
-      </c>
-      <c r="K6" s="47">
-        <v>0</v>
-      </c>
-      <c r="L6" s="47">
-        <v>0</v>
-      </c>
-      <c r="M6" s="47">
-        <v>0</v>
-      </c>
-      <c r="N6" s="47">
-        <v>0</v>
-      </c>
-      <c r="O6" s="47">
-        <v>0</v>
-      </c>
-      <c r="P6" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="47">
-        <v>0</v>
-      </c>
-      <c r="R6" s="47">
-        <v>0</v>
-      </c>
-      <c r="S6" s="47">
-        <v>0</v>
-      </c>
-      <c r="T6" s="47">
-        <v>0</v>
-      </c>
-      <c r="U6" s="47">
-        <v>0</v>
-      </c>
-      <c r="V6" s="47">
-        <v>0</v>
-      </c>
-      <c r="W6" s="47">
-        <v>0</v>
-      </c>
-      <c r="X6" s="47">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="47">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="47">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="47">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="47">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="47">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="47">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="47">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="47">
+      <c r="B6" s="149">
+        <v>0</v>
+      </c>
+      <c r="C6" s="149">
+        <v>0</v>
+      </c>
+      <c r="D6" s="149">
+        <v>0</v>
+      </c>
+      <c r="E6" s="149">
+        <v>0</v>
+      </c>
+      <c r="F6" s="149">
+        <v>0</v>
+      </c>
+      <c r="G6" s="149">
+        <v>0</v>
+      </c>
+      <c r="H6" s="149">
+        <v>0</v>
+      </c>
+      <c r="I6" s="149">
+        <v>0</v>
+      </c>
+      <c r="J6" s="149">
+        <v>0</v>
+      </c>
+      <c r="K6" s="149">
+        <v>0</v>
+      </c>
+      <c r="L6" s="149">
+        <v>0</v>
+      </c>
+      <c r="M6" s="149">
+        <v>0</v>
+      </c>
+      <c r="N6" s="149">
+        <v>0</v>
+      </c>
+      <c r="O6" s="149">
+        <v>0</v>
+      </c>
+      <c r="P6" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="149">
+        <v>0</v>
+      </c>
+      <c r="R6" s="149">
+        <v>0</v>
+      </c>
+      <c r="S6" s="149">
+        <v>0</v>
+      </c>
+      <c r="T6" s="149">
+        <v>0</v>
+      </c>
+      <c r="U6" s="149">
+        <v>0</v>
+      </c>
+      <c r="V6" s="149">
+        <v>0</v>
+      </c>
+      <c r="W6" s="149">
+        <v>0</v>
+      </c>
+      <c r="X6" s="149">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="149">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="149">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="149">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="149">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="149">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="149">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="149">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="149">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="149">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="149">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="149">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="149">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="149">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="149">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="149">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="149">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="149">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="149">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="149">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="149">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="149">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="149">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="149">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="149">
+        <v>0</v>
+      </c>
+      <c r="AW6" s="149">
+        <v>0</v>
+      </c>
+      <c r="AX6" s="149">
+        <v>0</v>
+      </c>
+      <c r="AY6" s="149">
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="149">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A7" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="47">
-        <v>0</v>
-      </c>
-      <c r="C7" s="47">
-        <v>0</v>
-      </c>
-      <c r="D7" s="47">
-        <v>0</v>
-      </c>
-      <c r="E7" s="47">
-        <v>0</v>
-      </c>
-      <c r="F7" s="47">
-        <v>0</v>
-      </c>
-      <c r="G7" s="47">
-        <v>0</v>
-      </c>
-      <c r="H7" s="47">
-        <v>0</v>
-      </c>
-      <c r="I7" s="47">
-        <v>0</v>
-      </c>
-      <c r="J7" s="47">
-        <v>0</v>
-      </c>
-      <c r="K7" s="47">
-        <v>0</v>
-      </c>
-      <c r="L7" s="47">
-        <v>0</v>
-      </c>
-      <c r="M7" s="47">
-        <v>0</v>
-      </c>
-      <c r="N7" s="47">
-        <v>0</v>
-      </c>
-      <c r="O7" s="47">
-        <v>0</v>
-      </c>
-      <c r="P7" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="47">
-        <v>0</v>
-      </c>
-      <c r="R7" s="47">
-        <v>0</v>
-      </c>
-      <c r="S7" s="47">
-        <v>0</v>
-      </c>
-      <c r="T7" s="47">
-        <v>0</v>
-      </c>
-      <c r="U7" s="47">
-        <v>0</v>
-      </c>
-      <c r="V7" s="47">
-        <v>0</v>
-      </c>
-      <c r="W7" s="47">
-        <v>0</v>
-      </c>
-      <c r="X7" s="47">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="47">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="47">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="47">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="47">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="47">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="47">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="47">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="47">
+      <c r="B7" s="149">
+        <v>0</v>
+      </c>
+      <c r="C7" s="149">
+        <v>0</v>
+      </c>
+      <c r="D7" s="149">
+        <v>0</v>
+      </c>
+      <c r="E7" s="149">
+        <v>0</v>
+      </c>
+      <c r="F7" s="149">
+        <v>0</v>
+      </c>
+      <c r="G7" s="149">
+        <v>0</v>
+      </c>
+      <c r="H7" s="149">
+        <v>0</v>
+      </c>
+      <c r="I7" s="149">
+        <v>0</v>
+      </c>
+      <c r="J7" s="149">
+        <v>0</v>
+      </c>
+      <c r="K7" s="149">
+        <v>0</v>
+      </c>
+      <c r="L7" s="149">
+        <v>0</v>
+      </c>
+      <c r="M7" s="149">
+        <v>0</v>
+      </c>
+      <c r="N7" s="149">
+        <v>0</v>
+      </c>
+      <c r="O7" s="149">
+        <v>0</v>
+      </c>
+      <c r="P7" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="149">
+        <v>0</v>
+      </c>
+      <c r="R7" s="149">
+        <v>0</v>
+      </c>
+      <c r="S7" s="149">
+        <v>0</v>
+      </c>
+      <c r="T7" s="149">
+        <v>0</v>
+      </c>
+      <c r="U7" s="149">
+        <v>0</v>
+      </c>
+      <c r="V7" s="149">
+        <v>0</v>
+      </c>
+      <c r="W7" s="149">
+        <v>0</v>
+      </c>
+      <c r="X7" s="149">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="149">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="149">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="149">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="149">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="149">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="149">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="149">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="149">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="149">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="149">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="149">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="149">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="149">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="149">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="149">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="149">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="149">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="149">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="149">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="149">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="149">
+        <v>0</v>
+      </c>
+      <c r="AT7" s="149">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="149">
+        <v>0</v>
+      </c>
+      <c r="AV7" s="149">
+        <v>0</v>
+      </c>
+      <c r="AW7" s="149">
+        <v>0</v>
+      </c>
+      <c r="AX7" s="149">
+        <v>0</v>
+      </c>
+      <c r="AY7" s="149">
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="149">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A8" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="47">
-        <v>0</v>
-      </c>
-      <c r="C8" s="47">
-        <v>0</v>
-      </c>
-      <c r="D8" s="47">
-        <v>0</v>
-      </c>
-      <c r="E8" s="47">
-        <v>0</v>
-      </c>
-      <c r="F8" s="47">
-        <v>0</v>
-      </c>
-      <c r="G8" s="47">
-        <v>0</v>
-      </c>
-      <c r="H8" s="47">
-        <v>0</v>
-      </c>
-      <c r="I8" s="47">
-        <v>0</v>
-      </c>
-      <c r="J8" s="47">
-        <v>0</v>
-      </c>
-      <c r="K8" s="47">
-        <v>0</v>
-      </c>
-      <c r="L8" s="47">
-        <v>0</v>
-      </c>
-      <c r="M8" s="47">
-        <v>0</v>
-      </c>
-      <c r="N8" s="47">
-        <v>0</v>
-      </c>
-      <c r="O8" s="47">
-        <v>0</v>
-      </c>
-      <c r="P8" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="47">
-        <v>0</v>
-      </c>
-      <c r="R8" s="47">
-        <v>0</v>
-      </c>
-      <c r="S8" s="47">
-        <v>0</v>
-      </c>
-      <c r="T8" s="47">
-        <v>0</v>
-      </c>
-      <c r="U8" s="47">
-        <v>0</v>
-      </c>
-      <c r="V8" s="47">
-        <v>0</v>
-      </c>
-      <c r="W8" s="47">
-        <v>0</v>
-      </c>
-      <c r="X8" s="47">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="47">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="47">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="47">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="47">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="47">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="47">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="47">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="47">
+      <c r="B8" s="149">
+        <v>0</v>
+      </c>
+      <c r="C8" s="149">
+        <v>0</v>
+      </c>
+      <c r="D8" s="149">
+        <v>0</v>
+      </c>
+      <c r="E8" s="149">
+        <v>0</v>
+      </c>
+      <c r="F8" s="149">
+        <v>0</v>
+      </c>
+      <c r="G8" s="149">
+        <v>0</v>
+      </c>
+      <c r="H8" s="149">
+        <v>0</v>
+      </c>
+      <c r="I8" s="149">
+        <v>0</v>
+      </c>
+      <c r="J8" s="149">
+        <v>0</v>
+      </c>
+      <c r="K8" s="149">
+        <v>0</v>
+      </c>
+      <c r="L8" s="149">
+        <v>0</v>
+      </c>
+      <c r="M8" s="149">
+        <v>0</v>
+      </c>
+      <c r="N8" s="149">
+        <v>0</v>
+      </c>
+      <c r="O8" s="149">
+        <v>0</v>
+      </c>
+      <c r="P8" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="149">
+        <v>0</v>
+      </c>
+      <c r="R8" s="149">
+        <v>0</v>
+      </c>
+      <c r="S8" s="149">
+        <v>0</v>
+      </c>
+      <c r="T8" s="149">
+        <v>0</v>
+      </c>
+      <c r="U8" s="149">
+        <v>0</v>
+      </c>
+      <c r="V8" s="149">
+        <v>0</v>
+      </c>
+      <c r="W8" s="149">
+        <v>0</v>
+      </c>
+      <c r="X8" s="149">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="149">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="149">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="149">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="149">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="149">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="149">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="149">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="149">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="149">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="149">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="149">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="149">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="149">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="149">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="149">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="149">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="149">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="149">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="149">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="149">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="149">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="149">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="149">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="149">
+        <v>0</v>
+      </c>
+      <c r="AW8" s="149">
+        <v>0</v>
+      </c>
+      <c r="AX8" s="149">
+        <v>0</v>
+      </c>
+      <c r="AY8" s="149">
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="149">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A9" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="47">
-        <v>0</v>
-      </c>
-      <c r="C9" s="47">
-        <v>0</v>
-      </c>
-      <c r="D9" s="47">
-        <v>0</v>
-      </c>
-      <c r="E9" s="47">
-        <v>0</v>
-      </c>
-      <c r="F9" s="47">
-        <v>0</v>
-      </c>
-      <c r="G9" s="47">
-        <v>0</v>
-      </c>
-      <c r="H9" s="47">
-        <v>0</v>
-      </c>
-      <c r="I9" s="47">
-        <v>0</v>
-      </c>
-      <c r="J9" s="47">
-        <v>0</v>
-      </c>
-      <c r="K9" s="47">
-        <v>0</v>
-      </c>
-      <c r="L9" s="47">
-        <v>0</v>
-      </c>
-      <c r="M9" s="47">
-        <v>0</v>
-      </c>
-      <c r="N9" s="47">
-        <v>0</v>
-      </c>
-      <c r="O9" s="47">
-        <v>0</v>
-      </c>
-      <c r="P9" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="47">
-        <v>0</v>
-      </c>
-      <c r="R9" s="47">
-        <v>0</v>
-      </c>
-      <c r="S9" s="47">
-        <v>0</v>
-      </c>
-      <c r="T9" s="47">
-        <v>0</v>
-      </c>
-      <c r="U9" s="47">
-        <v>0</v>
-      </c>
-      <c r="V9" s="47">
-        <v>0</v>
-      </c>
-      <c r="W9" s="47">
-        <v>0</v>
-      </c>
-      <c r="X9" s="47">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="47">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="47">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="47">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="47">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="47">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="47">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="47">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="47">
+      <c r="B9" s="149">
+        <v>0</v>
+      </c>
+      <c r="C9" s="149">
+        <v>0</v>
+      </c>
+      <c r="D9" s="149">
+        <v>0</v>
+      </c>
+      <c r="E9" s="149">
+        <v>0</v>
+      </c>
+      <c r="F9" s="149">
+        <v>0</v>
+      </c>
+      <c r="G9" s="149">
+        <v>0</v>
+      </c>
+      <c r="H9" s="149">
+        <v>0</v>
+      </c>
+      <c r="I9" s="149">
+        <v>0</v>
+      </c>
+      <c r="J9" s="149">
+        <v>0</v>
+      </c>
+      <c r="K9" s="149">
+        <v>0</v>
+      </c>
+      <c r="L9" s="149">
+        <v>0</v>
+      </c>
+      <c r="M9" s="149">
+        <v>0</v>
+      </c>
+      <c r="N9" s="149">
+        <v>0</v>
+      </c>
+      <c r="O9" s="149">
+        <v>0</v>
+      </c>
+      <c r="P9" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="149">
+        <v>0</v>
+      </c>
+      <c r="R9" s="149">
+        <v>0</v>
+      </c>
+      <c r="S9" s="149">
+        <v>0</v>
+      </c>
+      <c r="T9" s="149">
+        <v>0</v>
+      </c>
+      <c r="U9" s="149">
+        <v>0</v>
+      </c>
+      <c r="V9" s="149">
+        <v>0</v>
+      </c>
+      <c r="W9" s="149">
+        <v>0</v>
+      </c>
+      <c r="X9" s="149">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="149">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="149">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="149">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="149">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="149">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="149">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="149">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="149">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="149">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="149">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="149">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="149">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="149">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="149">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="149">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="149">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="149">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="149">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="149">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="149">
+        <v>0</v>
+      </c>
+      <c r="AS9" s="149">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="149">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="149">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="149">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="149">
+        <v>0</v>
+      </c>
+      <c r="AX9" s="149">
+        <v>0</v>
+      </c>
+      <c r="AY9" s="149">
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="149">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A10" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="47">
-        <v>0</v>
-      </c>
-      <c r="C10" s="47">
-        <v>0</v>
-      </c>
-      <c r="D10" s="47">
-        <v>0</v>
-      </c>
-      <c r="E10" s="47">
-        <v>0</v>
-      </c>
-      <c r="F10" s="47">
-        <v>0</v>
-      </c>
-      <c r="G10" s="47">
-        <v>0</v>
-      </c>
-      <c r="H10" s="47">
-        <v>0</v>
-      </c>
-      <c r="I10" s="47">
-        <v>0</v>
-      </c>
-      <c r="J10" s="47">
-        <v>0</v>
-      </c>
-      <c r="K10" s="47">
-        <v>0</v>
-      </c>
-      <c r="L10" s="47">
-        <v>0</v>
-      </c>
-      <c r="M10" s="47">
-        <v>0</v>
-      </c>
-      <c r="N10" s="47">
-        <v>0</v>
-      </c>
-      <c r="O10" s="47">
-        <v>0</v>
-      </c>
-      <c r="P10" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="47">
-        <v>0</v>
-      </c>
-      <c r="R10" s="47">
-        <v>0</v>
-      </c>
-      <c r="S10" s="47">
-        <v>0</v>
-      </c>
-      <c r="T10" s="47">
-        <v>0</v>
-      </c>
-      <c r="U10" s="47">
-        <v>0</v>
-      </c>
-      <c r="V10" s="47">
-        <v>0</v>
-      </c>
-      <c r="W10" s="47">
-        <v>0</v>
-      </c>
-      <c r="X10" s="47">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="47">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="47">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="47">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="47">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="47">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="47">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="47">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="47">
+      <c r="B10" s="149">
+        <v>0</v>
+      </c>
+      <c r="C10" s="149">
+        <v>0</v>
+      </c>
+      <c r="D10" s="149">
+        <v>0</v>
+      </c>
+      <c r="E10" s="149">
+        <v>0</v>
+      </c>
+      <c r="F10" s="149">
+        <v>0</v>
+      </c>
+      <c r="G10" s="149">
+        <v>0</v>
+      </c>
+      <c r="H10" s="149">
+        <v>0</v>
+      </c>
+      <c r="I10" s="149">
+        <v>0</v>
+      </c>
+      <c r="J10" s="149">
+        <v>0</v>
+      </c>
+      <c r="K10" s="149">
+        <v>0</v>
+      </c>
+      <c r="L10" s="149">
+        <v>0</v>
+      </c>
+      <c r="M10" s="149">
+        <v>0</v>
+      </c>
+      <c r="N10" s="149">
+        <v>0</v>
+      </c>
+      <c r="O10" s="149">
+        <v>0</v>
+      </c>
+      <c r="P10" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="149">
+        <v>0</v>
+      </c>
+      <c r="R10" s="149">
+        <v>0</v>
+      </c>
+      <c r="S10" s="149">
+        <v>0</v>
+      </c>
+      <c r="T10" s="149">
+        <v>0</v>
+      </c>
+      <c r="U10" s="149">
+        <v>0</v>
+      </c>
+      <c r="V10" s="149">
+        <v>0</v>
+      </c>
+      <c r="W10" s="149">
+        <v>0</v>
+      </c>
+      <c r="X10" s="149">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="149">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="149">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="149">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="149">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="149">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="149">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="149">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="149">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="149">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="149">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="149">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="149">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="149">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="149">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="149">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="149">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="149">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="149">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="149">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="149">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="149">
+        <v>0</v>
+      </c>
+      <c r="AT10" s="149">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="149">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="149">
+        <v>0</v>
+      </c>
+      <c r="AW10" s="149">
+        <v>0</v>
+      </c>
+      <c r="AX10" s="149">
+        <v>0</v>
+      </c>
+      <c r="AY10" s="149">
+        <v>0</v>
+      </c>
+      <c r="AZ10" s="149">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A11" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="47">
-        <v>0</v>
-      </c>
-      <c r="C11" s="47">
-        <v>0</v>
-      </c>
-      <c r="D11" s="47">
-        <v>0</v>
-      </c>
-      <c r="E11" s="47">
-        <v>0</v>
-      </c>
-      <c r="F11" s="47">
-        <v>0</v>
-      </c>
-      <c r="G11" s="47">
-        <v>0</v>
-      </c>
-      <c r="H11" s="47">
-        <v>0</v>
-      </c>
-      <c r="I11" s="47">
-        <v>0</v>
-      </c>
-      <c r="J11" s="47">
-        <v>0</v>
-      </c>
-      <c r="K11" s="47">
-        <v>0</v>
-      </c>
-      <c r="L11" s="47">
-        <v>0</v>
-      </c>
-      <c r="M11" s="47">
-        <v>0</v>
-      </c>
-      <c r="N11" s="47">
-        <v>0</v>
-      </c>
-      <c r="O11" s="47">
-        <v>0</v>
-      </c>
-      <c r="P11" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="47">
-        <v>0</v>
-      </c>
-      <c r="R11" s="47">
-        <v>0</v>
-      </c>
-      <c r="S11" s="47">
-        <v>0</v>
-      </c>
-      <c r="T11" s="47">
-        <v>0</v>
-      </c>
-      <c r="U11" s="47">
-        <v>0</v>
-      </c>
-      <c r="V11" s="47">
-        <v>0</v>
-      </c>
-      <c r="W11" s="47">
-        <v>0</v>
-      </c>
-      <c r="X11" s="47">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="47">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="47">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="47">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="47">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="47">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="47">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="47">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="47">
+      <c r="B11" s="149">
+        <v>0</v>
+      </c>
+      <c r="C11" s="149">
+        <v>0</v>
+      </c>
+      <c r="D11" s="149">
+        <v>0</v>
+      </c>
+      <c r="E11" s="149">
+        <v>0</v>
+      </c>
+      <c r="F11" s="149">
+        <v>0</v>
+      </c>
+      <c r="G11" s="149">
+        <v>0</v>
+      </c>
+      <c r="H11" s="149">
+        <v>0</v>
+      </c>
+      <c r="I11" s="149">
+        <v>0</v>
+      </c>
+      <c r="J11" s="149">
+        <v>0</v>
+      </c>
+      <c r="K11" s="149">
+        <v>0</v>
+      </c>
+      <c r="L11" s="149">
+        <v>0</v>
+      </c>
+      <c r="M11" s="149">
+        <v>0</v>
+      </c>
+      <c r="N11" s="149">
+        <v>0</v>
+      </c>
+      <c r="O11" s="149">
+        <v>0</v>
+      </c>
+      <c r="P11" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="149">
+        <v>0</v>
+      </c>
+      <c r="R11" s="149">
+        <v>0</v>
+      </c>
+      <c r="S11" s="149">
+        <v>0</v>
+      </c>
+      <c r="T11" s="149">
+        <v>0</v>
+      </c>
+      <c r="U11" s="149">
+        <v>0</v>
+      </c>
+      <c r="V11" s="149">
+        <v>0</v>
+      </c>
+      <c r="W11" s="149">
+        <v>0</v>
+      </c>
+      <c r="X11" s="149">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="149">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="149">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="149">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="149">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="149">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="149">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="149">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="149">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="149">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="149">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="149">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="149">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="149">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="149">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="149">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="149">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="149">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="149">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="149">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="149">
+        <v>0</v>
+      </c>
+      <c r="AS11" s="149">
+        <v>0</v>
+      </c>
+      <c r="AT11" s="149">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="149">
+        <v>0</v>
+      </c>
+      <c r="AV11" s="149">
+        <v>0</v>
+      </c>
+      <c r="AW11" s="149">
+        <v>0</v>
+      </c>
+      <c r="AX11" s="149">
+        <v>0</v>
+      </c>
+      <c r="AY11" s="149">
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="149">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A12" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="47">
-        <v>0</v>
-      </c>
-      <c r="C12" s="47">
-        <v>0</v>
-      </c>
-      <c r="D12" s="47">
-        <v>0</v>
-      </c>
-      <c r="E12" s="47">
-        <v>0</v>
-      </c>
-      <c r="F12" s="47">
-        <v>0</v>
-      </c>
-      <c r="G12" s="47">
-        <v>0</v>
-      </c>
-      <c r="H12" s="47">
-        <v>0</v>
-      </c>
-      <c r="I12" s="47">
-        <v>0</v>
-      </c>
-      <c r="J12" s="47">
-        <v>0</v>
-      </c>
-      <c r="K12" s="47">
-        <v>0</v>
-      </c>
-      <c r="L12" s="47">
-        <v>0</v>
-      </c>
-      <c r="M12" s="47">
-        <v>0</v>
-      </c>
-      <c r="N12" s="47">
-        <v>0</v>
-      </c>
-      <c r="O12" s="47">
-        <v>0</v>
-      </c>
-      <c r="P12" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="47">
-        <v>0</v>
-      </c>
-      <c r="R12" s="47">
-        <v>0</v>
-      </c>
-      <c r="S12" s="47">
-        <v>0</v>
-      </c>
-      <c r="T12" s="47">
-        <v>0</v>
-      </c>
-      <c r="U12" s="47">
-        <v>0</v>
-      </c>
-      <c r="V12" s="47">
-        <v>0</v>
-      </c>
-      <c r="W12" s="47">
-        <v>0</v>
-      </c>
-      <c r="X12" s="47">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="47">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="47">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="47">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="47">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="47">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="47">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="47">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="47">
+      <c r="B12" s="149">
+        <v>0</v>
+      </c>
+      <c r="C12" s="149">
+        <v>0</v>
+      </c>
+      <c r="D12" s="149">
+        <v>0</v>
+      </c>
+      <c r="E12" s="149">
+        <v>0</v>
+      </c>
+      <c r="F12" s="149">
+        <v>0</v>
+      </c>
+      <c r="G12" s="149">
+        <v>0</v>
+      </c>
+      <c r="H12" s="149">
+        <v>0</v>
+      </c>
+      <c r="I12" s="149">
+        <v>0</v>
+      </c>
+      <c r="J12" s="149">
+        <v>0</v>
+      </c>
+      <c r="K12" s="149">
+        <v>0</v>
+      </c>
+      <c r="L12" s="149">
+        <v>0</v>
+      </c>
+      <c r="M12" s="149">
+        <v>0</v>
+      </c>
+      <c r="N12" s="149">
+        <v>0</v>
+      </c>
+      <c r="O12" s="149">
+        <v>0</v>
+      </c>
+      <c r="P12" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="149">
+        <v>0</v>
+      </c>
+      <c r="R12" s="149">
+        <v>0</v>
+      </c>
+      <c r="S12" s="149">
+        <v>0</v>
+      </c>
+      <c r="T12" s="149">
+        <v>0</v>
+      </c>
+      <c r="U12" s="149">
+        <v>0</v>
+      </c>
+      <c r="V12" s="149">
+        <v>0</v>
+      </c>
+      <c r="W12" s="149">
+        <v>0</v>
+      </c>
+      <c r="X12" s="149">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="149">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="149">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="149">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="149">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="149">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="149">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="149">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="149">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="149">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="149">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="149">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="149">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="149">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="149">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="149">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="149">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="149">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="149">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="149">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="149">
+        <v>0</v>
+      </c>
+      <c r="AS12" s="149">
+        <v>0</v>
+      </c>
+      <c r="AT12" s="149">
+        <v>0</v>
+      </c>
+      <c r="AU12" s="149">
+        <v>0</v>
+      </c>
+      <c r="AV12" s="149">
+        <v>0</v>
+      </c>
+      <c r="AW12" s="149">
+        <v>0</v>
+      </c>
+      <c r="AX12" s="149">
+        <v>0</v>
+      </c>
+      <c r="AY12" s="149">
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="149">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A13" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="47">
-        <v>0</v>
-      </c>
-      <c r="C13" s="47">
-        <v>0</v>
-      </c>
-      <c r="D13" s="47">
-        <v>0</v>
-      </c>
-      <c r="E13" s="47">
-        <v>0</v>
-      </c>
-      <c r="F13" s="47">
-        <v>0</v>
-      </c>
-      <c r="G13" s="47">
-        <v>0</v>
-      </c>
-      <c r="H13" s="47">
-        <v>0</v>
-      </c>
-      <c r="I13" s="47">
-        <v>0</v>
-      </c>
-      <c r="J13" s="47">
-        <v>0</v>
-      </c>
-      <c r="K13" s="47">
-        <v>0</v>
-      </c>
-      <c r="L13" s="47">
-        <v>0</v>
-      </c>
-      <c r="M13" s="47">
-        <v>0</v>
-      </c>
-      <c r="N13" s="47">
-        <v>0</v>
-      </c>
-      <c r="O13" s="47">
-        <v>0</v>
-      </c>
-      <c r="P13" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="47">
-        <v>0</v>
-      </c>
-      <c r="R13" s="47">
-        <v>0</v>
-      </c>
-      <c r="S13" s="47">
-        <v>0</v>
-      </c>
-      <c r="T13" s="47">
-        <v>0</v>
-      </c>
-      <c r="U13" s="47">
-        <v>0</v>
-      </c>
-      <c r="V13" s="47">
-        <v>0</v>
-      </c>
-      <c r="W13" s="47">
-        <v>0</v>
-      </c>
-      <c r="X13" s="47">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="47">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="47">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="47">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="47">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="47">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="47">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="47">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="47">
+      <c r="B13" s="149">
+        <v>0</v>
+      </c>
+      <c r="C13" s="149">
+        <v>0</v>
+      </c>
+      <c r="D13" s="149">
+        <v>0</v>
+      </c>
+      <c r="E13" s="149">
+        <v>0</v>
+      </c>
+      <c r="F13" s="149">
+        <v>0</v>
+      </c>
+      <c r="G13" s="149">
+        <v>0</v>
+      </c>
+      <c r="H13" s="149">
+        <v>0</v>
+      </c>
+      <c r="I13" s="149">
+        <v>0</v>
+      </c>
+      <c r="J13" s="149">
+        <v>0</v>
+      </c>
+      <c r="K13" s="149">
+        <v>0</v>
+      </c>
+      <c r="L13" s="149">
+        <v>0</v>
+      </c>
+      <c r="M13" s="149">
+        <v>0</v>
+      </c>
+      <c r="N13" s="149">
+        <v>0</v>
+      </c>
+      <c r="O13" s="149">
+        <v>0</v>
+      </c>
+      <c r="P13" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="149">
+        <v>0</v>
+      </c>
+      <c r="R13" s="149">
+        <v>0</v>
+      </c>
+      <c r="S13" s="149">
+        <v>0</v>
+      </c>
+      <c r="T13" s="149">
+        <v>0</v>
+      </c>
+      <c r="U13" s="149">
+        <v>0</v>
+      </c>
+      <c r="V13" s="149">
+        <v>0</v>
+      </c>
+      <c r="W13" s="149">
+        <v>0</v>
+      </c>
+      <c r="X13" s="149">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="149">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="149">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="149">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="149">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="149">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="149">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="149">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="149">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="149">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="149">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="149">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="149">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="149">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="149">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="149">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="149">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="149">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="149">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="149">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="149">
+        <v>0</v>
+      </c>
+      <c r="AS13" s="149">
+        <v>0</v>
+      </c>
+      <c r="AT13" s="149">
+        <v>0</v>
+      </c>
+      <c r="AU13" s="149">
+        <v>0</v>
+      </c>
+      <c r="AV13" s="149">
+        <v>0</v>
+      </c>
+      <c r="AW13" s="149">
+        <v>0</v>
+      </c>
+      <c r="AX13" s="149">
+        <v>0</v>
+      </c>
+      <c r="AY13" s="149">
+        <v>0</v>
+      </c>
+      <c r="AZ13" s="149">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A14" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="47">
-        <v>0</v>
-      </c>
-      <c r="C14" s="47">
-        <v>0</v>
-      </c>
-      <c r="D14" s="47">
-        <v>0</v>
-      </c>
-      <c r="E14" s="47">
-        <v>0</v>
-      </c>
-      <c r="F14" s="47">
-        <v>0</v>
-      </c>
-      <c r="G14" s="47">
-        <v>0</v>
-      </c>
-      <c r="H14" s="47">
-        <v>0</v>
-      </c>
-      <c r="I14" s="47">
-        <v>0</v>
-      </c>
-      <c r="J14" s="47">
-        <v>0</v>
-      </c>
-      <c r="K14" s="47">
-        <v>0</v>
-      </c>
-      <c r="L14" s="47">
-        <v>0</v>
-      </c>
-      <c r="M14" s="47">
-        <v>0</v>
-      </c>
-      <c r="N14" s="47">
-        <v>0</v>
-      </c>
-      <c r="O14" s="47">
-        <v>0</v>
-      </c>
-      <c r="P14" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="47">
-        <v>0</v>
-      </c>
-      <c r="R14" s="47">
-        <v>0</v>
-      </c>
-      <c r="S14" s="47">
-        <v>0</v>
-      </c>
-      <c r="T14" s="47">
-        <v>0</v>
-      </c>
-      <c r="U14" s="47">
-        <v>0</v>
-      </c>
-      <c r="V14" s="47">
-        <v>0</v>
-      </c>
-      <c r="W14" s="47">
-        <v>0</v>
-      </c>
-      <c r="X14" s="47">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="47">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="47">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="47">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="47">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="47">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="47">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="47">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="47">
+      <c r="B14" s="149">
+        <v>0</v>
+      </c>
+      <c r="C14" s="149">
+        <v>0</v>
+      </c>
+      <c r="D14" s="149">
+        <v>0</v>
+      </c>
+      <c r="E14" s="149">
+        <v>0</v>
+      </c>
+      <c r="F14" s="149">
+        <v>0</v>
+      </c>
+      <c r="G14" s="149">
+        <v>0</v>
+      </c>
+      <c r="H14" s="149">
+        <v>0</v>
+      </c>
+      <c r="I14" s="149">
+        <v>0</v>
+      </c>
+      <c r="J14" s="149">
+        <v>0</v>
+      </c>
+      <c r="K14" s="149">
+        <v>0</v>
+      </c>
+      <c r="L14" s="149">
+        <v>0</v>
+      </c>
+      <c r="M14" s="149">
+        <v>0</v>
+      </c>
+      <c r="N14" s="149">
+        <v>0</v>
+      </c>
+      <c r="O14" s="149">
+        <v>0</v>
+      </c>
+      <c r="P14" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="149">
+        <v>0</v>
+      </c>
+      <c r="R14" s="149">
+        <v>0</v>
+      </c>
+      <c r="S14" s="149">
+        <v>0</v>
+      </c>
+      <c r="T14" s="149">
+        <v>0</v>
+      </c>
+      <c r="U14" s="149">
+        <v>0</v>
+      </c>
+      <c r="V14" s="149">
+        <v>0</v>
+      </c>
+      <c r="W14" s="149">
+        <v>0</v>
+      </c>
+      <c r="X14" s="149">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="149">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="149">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="149">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="149">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="149">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="149">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="149">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="149">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="149">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="149">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="149">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="149">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="149">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="149">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="149">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="149">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="149">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="149">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="149">
+        <v>0</v>
+      </c>
+      <c r="AR14" s="149">
+        <v>0</v>
+      </c>
+      <c r="AS14" s="149">
+        <v>0</v>
+      </c>
+      <c r="AT14" s="149">
+        <v>0</v>
+      </c>
+      <c r="AU14" s="149">
+        <v>0</v>
+      </c>
+      <c r="AV14" s="149">
+        <v>0</v>
+      </c>
+      <c r="AW14" s="149">
+        <v>0</v>
+      </c>
+      <c r="AX14" s="149">
+        <v>0</v>
+      </c>
+      <c r="AY14" s="149">
+        <v>0</v>
+      </c>
+      <c r="AZ14" s="149">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A15" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="47">
-        <v>0</v>
-      </c>
-      <c r="C15" s="47">
-        <v>0</v>
-      </c>
-      <c r="D15" s="47">
-        <v>0</v>
-      </c>
-      <c r="E15" s="47">
-        <v>0</v>
-      </c>
-      <c r="F15" s="47">
-        <v>0</v>
-      </c>
-      <c r="G15" s="47">
-        <v>0</v>
-      </c>
-      <c r="H15" s="47">
-        <v>0</v>
-      </c>
-      <c r="I15" s="47">
-        <v>0</v>
-      </c>
-      <c r="J15" s="47">
-        <v>0</v>
-      </c>
-      <c r="K15" s="47">
-        <v>0</v>
-      </c>
-      <c r="L15" s="47">
-        <v>0</v>
-      </c>
-      <c r="M15" s="47">
-        <v>0</v>
-      </c>
-      <c r="N15" s="47">
-        <v>0</v>
-      </c>
-      <c r="O15" s="47">
-        <v>0</v>
-      </c>
-      <c r="P15" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="47">
-        <v>0</v>
-      </c>
-      <c r="R15" s="47">
-        <v>0</v>
-      </c>
-      <c r="S15" s="47">
-        <v>0</v>
-      </c>
-      <c r="T15" s="47">
-        <v>0</v>
-      </c>
-      <c r="U15" s="47">
-        <v>0</v>
-      </c>
-      <c r="V15" s="47">
-        <v>0</v>
-      </c>
-      <c r="W15" s="47">
-        <v>0</v>
-      </c>
-      <c r="X15" s="47">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="47">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="47">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="47">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="47">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="47">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="47">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="47">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="47">
+      <c r="B15" s="149">
+        <v>0</v>
+      </c>
+      <c r="C15" s="149">
+        <v>0</v>
+      </c>
+      <c r="D15" s="149">
+        <v>0</v>
+      </c>
+      <c r="E15" s="149">
+        <v>0</v>
+      </c>
+      <c r="F15" s="149">
+        <v>0</v>
+      </c>
+      <c r="G15" s="149">
+        <v>0</v>
+      </c>
+      <c r="H15" s="149">
+        <v>0</v>
+      </c>
+      <c r="I15" s="149">
+        <v>0</v>
+      </c>
+      <c r="J15" s="149">
+        <v>0</v>
+      </c>
+      <c r="K15" s="149">
+        <v>0</v>
+      </c>
+      <c r="L15" s="149">
+        <v>0</v>
+      </c>
+      <c r="M15" s="149">
+        <v>0</v>
+      </c>
+      <c r="N15" s="149">
+        <v>0</v>
+      </c>
+      <c r="O15" s="149">
+        <v>0</v>
+      </c>
+      <c r="P15" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="149">
+        <v>0</v>
+      </c>
+      <c r="R15" s="149">
+        <v>0</v>
+      </c>
+      <c r="S15" s="149">
+        <v>0</v>
+      </c>
+      <c r="T15" s="149">
+        <v>0</v>
+      </c>
+      <c r="U15" s="149">
+        <v>0</v>
+      </c>
+      <c r="V15" s="149">
+        <v>0</v>
+      </c>
+      <c r="W15" s="149">
+        <v>0</v>
+      </c>
+      <c r="X15" s="149">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="149">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="149">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="149">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="149">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="149">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="149">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="149">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="149">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="149">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="149">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="149">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="149">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="149">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="149">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="149">
+        <v>0</v>
+      </c>
+      <c r="AN15" s="149">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="149">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="149">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="149">
+        <v>0</v>
+      </c>
+      <c r="AR15" s="149">
+        <v>0</v>
+      </c>
+      <c r="AS15" s="149">
+        <v>0</v>
+      </c>
+      <c r="AT15" s="149">
+        <v>0</v>
+      </c>
+      <c r="AU15" s="149">
+        <v>0</v>
+      </c>
+      <c r="AV15" s="149">
+        <v>0</v>
+      </c>
+      <c r="AW15" s="149">
+        <v>0</v>
+      </c>
+      <c r="AX15" s="149">
+        <v>0</v>
+      </c>
+      <c r="AY15" s="149">
+        <v>0</v>
+      </c>
+      <c r="AZ15" s="149">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A16" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="47">
-        <v>0</v>
-      </c>
-      <c r="C16" s="47">
-        <v>0</v>
-      </c>
-      <c r="D16" s="47">
-        <v>0</v>
-      </c>
-      <c r="E16" s="47">
-        <v>0</v>
-      </c>
-      <c r="F16" s="47">
-        <v>0</v>
-      </c>
-      <c r="G16" s="47">
-        <v>0</v>
-      </c>
-      <c r="H16" s="47">
-        <v>0</v>
-      </c>
-      <c r="I16" s="47">
-        <v>0</v>
-      </c>
-      <c r="J16" s="47">
-        <v>0</v>
-      </c>
-      <c r="K16" s="47">
-        <v>0</v>
-      </c>
-      <c r="L16" s="47">
-        <v>0</v>
-      </c>
-      <c r="M16" s="47">
-        <v>0</v>
-      </c>
-      <c r="N16" s="47">
-        <v>0</v>
-      </c>
-      <c r="O16" s="47">
-        <v>0</v>
-      </c>
-      <c r="P16" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="47">
-        <v>0</v>
-      </c>
-      <c r="R16" s="47">
-        <v>0</v>
-      </c>
-      <c r="S16" s="47">
-        <v>0</v>
-      </c>
-      <c r="T16" s="47">
-        <v>0</v>
-      </c>
-      <c r="U16" s="47">
-        <v>0</v>
-      </c>
-      <c r="V16" s="47">
-        <v>0</v>
-      </c>
-      <c r="W16" s="47">
-        <v>0</v>
-      </c>
-      <c r="X16" s="47">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="47">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="47">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="47">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="47">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="47">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="47">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="47">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="47">
+      <c r="B16" s="149">
+        <v>0</v>
+      </c>
+      <c r="C16" s="149">
+        <v>0</v>
+      </c>
+      <c r="D16" s="149">
+        <v>0</v>
+      </c>
+      <c r="E16" s="149">
+        <v>0</v>
+      </c>
+      <c r="F16" s="149">
+        <v>0</v>
+      </c>
+      <c r="G16" s="149">
+        <v>0</v>
+      </c>
+      <c r="H16" s="149">
+        <v>0</v>
+      </c>
+      <c r="I16" s="149">
+        <v>0</v>
+      </c>
+      <c r="J16" s="149">
+        <v>0</v>
+      </c>
+      <c r="K16" s="149">
+        <v>0</v>
+      </c>
+      <c r="L16" s="149">
+        <v>0</v>
+      </c>
+      <c r="M16" s="149">
+        <v>0</v>
+      </c>
+      <c r="N16" s="149">
+        <v>0</v>
+      </c>
+      <c r="O16" s="149">
+        <v>0</v>
+      </c>
+      <c r="P16" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="149">
+        <v>0</v>
+      </c>
+      <c r="R16" s="149">
+        <v>0</v>
+      </c>
+      <c r="S16" s="149">
+        <v>0</v>
+      </c>
+      <c r="T16" s="149">
+        <v>0</v>
+      </c>
+      <c r="U16" s="149">
+        <v>0</v>
+      </c>
+      <c r="V16" s="149">
+        <v>0</v>
+      </c>
+      <c r="W16" s="149">
+        <v>0</v>
+      </c>
+      <c r="X16" s="149">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="149">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="149">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="149">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="149">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="149">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="149">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="149">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="149">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="149">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="149">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="149">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="149">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="149">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="149">
+        <v>0</v>
+      </c>
+      <c r="AM16" s="149">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="149">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="149">
+        <v>0</v>
+      </c>
+      <c r="AP16" s="149">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="149">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="149">
+        <v>0</v>
+      </c>
+      <c r="AS16" s="149">
+        <v>0</v>
+      </c>
+      <c r="AT16" s="149">
+        <v>0</v>
+      </c>
+      <c r="AU16" s="149">
+        <v>0</v>
+      </c>
+      <c r="AV16" s="149">
+        <v>0</v>
+      </c>
+      <c r="AW16" s="149">
+        <v>0</v>
+      </c>
+      <c r="AX16" s="149">
+        <v>0</v>
+      </c>
+      <c r="AY16" s="149">
+        <v>0</v>
+      </c>
+      <c r="AZ16" s="149">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A17" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="47">
-        <v>0</v>
-      </c>
-      <c r="C17" s="47">
-        <v>0</v>
-      </c>
-      <c r="D17" s="47">
-        <v>0</v>
-      </c>
-      <c r="E17" s="47">
-        <v>0</v>
-      </c>
-      <c r="F17" s="47">
-        <v>0</v>
-      </c>
-      <c r="G17" s="47">
-        <v>0</v>
-      </c>
-      <c r="H17" s="47">
-        <v>0</v>
-      </c>
-      <c r="I17" s="47">
-        <v>0</v>
-      </c>
-      <c r="J17" s="47">
-        <v>0</v>
-      </c>
-      <c r="K17" s="47">
-        <v>0</v>
-      </c>
-      <c r="L17" s="47">
-        <v>0</v>
-      </c>
-      <c r="M17" s="47">
-        <v>0</v>
-      </c>
-      <c r="N17" s="47">
-        <v>0</v>
-      </c>
-      <c r="O17" s="47">
-        <v>0</v>
-      </c>
-      <c r="P17" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="47">
-        <v>0</v>
-      </c>
-      <c r="R17" s="47">
-        <v>0</v>
-      </c>
-      <c r="S17" s="47">
-        <v>0</v>
-      </c>
-      <c r="T17" s="47">
-        <v>0</v>
-      </c>
-      <c r="U17" s="47">
-        <v>0</v>
-      </c>
-      <c r="V17" s="47">
-        <v>0</v>
-      </c>
-      <c r="W17" s="47">
-        <v>0</v>
-      </c>
-      <c r="X17" s="47">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="47">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="47">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="47">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="47">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="47">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="47">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="47">
-        <v>0</v>
-      </c>
-      <c r="AF17" s="47">
+      <c r="B17" s="149">
+        <v>0</v>
+      </c>
+      <c r="C17" s="149">
+        <v>0</v>
+      </c>
+      <c r="D17" s="149">
+        <v>0</v>
+      </c>
+      <c r="E17" s="149">
+        <v>0</v>
+      </c>
+      <c r="F17" s="149">
+        <v>0</v>
+      </c>
+      <c r="G17" s="149">
+        <v>0</v>
+      </c>
+      <c r="H17" s="149">
+        <v>0</v>
+      </c>
+      <c r="I17" s="149">
+        <v>0</v>
+      </c>
+      <c r="J17" s="149">
+        <v>0</v>
+      </c>
+      <c r="K17" s="149">
+        <v>0</v>
+      </c>
+      <c r="L17" s="149">
+        <v>0</v>
+      </c>
+      <c r="M17" s="149">
+        <v>0</v>
+      </c>
+      <c r="N17" s="149">
+        <v>0</v>
+      </c>
+      <c r="O17" s="149">
+        <v>0</v>
+      </c>
+      <c r="P17" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="149">
+        <v>0</v>
+      </c>
+      <c r="R17" s="149">
+        <v>0</v>
+      </c>
+      <c r="S17" s="149">
+        <v>0</v>
+      </c>
+      <c r="T17" s="149">
+        <v>0</v>
+      </c>
+      <c r="U17" s="149">
+        <v>0</v>
+      </c>
+      <c r="V17" s="149">
+        <v>0</v>
+      </c>
+      <c r="W17" s="149">
+        <v>0</v>
+      </c>
+      <c r="X17" s="149">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="149">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="149">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="149">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="149">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="149">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="149">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="149">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="149">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="149">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="149">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="149">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="149">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="149">
+        <v>0</v>
+      </c>
+      <c r="AL17" s="149">
+        <v>0</v>
+      </c>
+      <c r="AM17" s="149">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="149">
+        <v>0</v>
+      </c>
+      <c r="AO17" s="149">
+        <v>0</v>
+      </c>
+      <c r="AP17" s="149">
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="149">
+        <v>0</v>
+      </c>
+      <c r="AR17" s="149">
+        <v>0</v>
+      </c>
+      <c r="AS17" s="149">
+        <v>0</v>
+      </c>
+      <c r="AT17" s="149">
+        <v>0</v>
+      </c>
+      <c r="AU17" s="149">
+        <v>0</v>
+      </c>
+      <c r="AV17" s="149">
+        <v>0</v>
+      </c>
+      <c r="AW17" s="149">
+        <v>0</v>
+      </c>
+      <c r="AX17" s="149">
+        <v>0</v>
+      </c>
+      <c r="AY17" s="149">
+        <v>0</v>
+      </c>
+      <c r="AZ17" s="149">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A18" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="47">
-        <v>0</v>
-      </c>
-      <c r="C18" s="47">
-        <v>0</v>
-      </c>
-      <c r="D18" s="47">
-        <v>0</v>
-      </c>
-      <c r="E18" s="47">
-        <v>0</v>
-      </c>
-      <c r="F18" s="47">
-        <v>0</v>
-      </c>
-      <c r="G18" s="47">
-        <v>0</v>
-      </c>
-      <c r="H18" s="47">
-        <v>0</v>
-      </c>
-      <c r="I18" s="47">
-        <v>0</v>
-      </c>
-      <c r="J18" s="47">
-        <v>0</v>
-      </c>
-      <c r="K18" s="47">
-        <v>0</v>
-      </c>
-      <c r="L18" s="47">
-        <v>0</v>
-      </c>
-      <c r="M18" s="47">
-        <v>0</v>
-      </c>
-      <c r="N18" s="47">
-        <v>0</v>
-      </c>
-      <c r="O18" s="47">
-        <v>0</v>
-      </c>
-      <c r="P18" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="47">
-        <v>0</v>
-      </c>
-      <c r="R18" s="47">
-        <v>0</v>
-      </c>
-      <c r="S18" s="47">
-        <v>0</v>
-      </c>
-      <c r="T18" s="47">
-        <v>0</v>
-      </c>
-      <c r="U18" s="47">
-        <v>0</v>
-      </c>
-      <c r="V18" s="47">
-        <v>0</v>
-      </c>
-      <c r="W18" s="47">
-        <v>0</v>
-      </c>
-      <c r="X18" s="47">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="47">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="47">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="47">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="47">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="47">
-        <v>0</v>
-      </c>
-      <c r="AD18" s="47">
-        <v>0</v>
-      </c>
-      <c r="AE18" s="47">
-        <v>0</v>
-      </c>
-      <c r="AF18" s="47">
+      <c r="B18" s="149">
+        <v>0</v>
+      </c>
+      <c r="C18" s="149">
+        <v>0</v>
+      </c>
+      <c r="D18" s="149">
+        <v>0</v>
+      </c>
+      <c r="E18" s="149">
+        <v>0</v>
+      </c>
+      <c r="F18" s="149">
+        <v>0</v>
+      </c>
+      <c r="G18" s="149">
+        <v>0</v>
+      </c>
+      <c r="H18" s="149">
+        <v>0</v>
+      </c>
+      <c r="I18" s="149">
+        <v>0</v>
+      </c>
+      <c r="J18" s="149">
+        <v>0</v>
+      </c>
+      <c r="K18" s="149">
+        <v>0</v>
+      </c>
+      <c r="L18" s="149">
+        <v>0</v>
+      </c>
+      <c r="M18" s="149">
+        <v>0</v>
+      </c>
+      <c r="N18" s="149">
+        <v>0</v>
+      </c>
+      <c r="O18" s="149">
+        <v>0</v>
+      </c>
+      <c r="P18" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="149">
+        <v>0</v>
+      </c>
+      <c r="R18" s="149">
+        <v>0</v>
+      </c>
+      <c r="S18" s="149">
+        <v>0</v>
+      </c>
+      <c r="T18" s="149">
+        <v>0</v>
+      </c>
+      <c r="U18" s="149">
+        <v>0</v>
+      </c>
+      <c r="V18" s="149">
+        <v>0</v>
+      </c>
+      <c r="W18" s="149">
+        <v>0</v>
+      </c>
+      <c r="X18" s="149">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="149">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="149">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="149">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="149">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="149">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="149">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="149">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="149">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="149">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="149">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="149">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="149">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="149">
+        <v>0</v>
+      </c>
+      <c r="AL18" s="149">
+        <v>0</v>
+      </c>
+      <c r="AM18" s="149">
+        <v>0</v>
+      </c>
+      <c r="AN18" s="149">
+        <v>0</v>
+      </c>
+      <c r="AO18" s="149">
+        <v>0</v>
+      </c>
+      <c r="AP18" s="149">
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="149">
+        <v>0</v>
+      </c>
+      <c r="AR18" s="149">
+        <v>0</v>
+      </c>
+      <c r="AS18" s="149">
+        <v>0</v>
+      </c>
+      <c r="AT18" s="149">
+        <v>0</v>
+      </c>
+      <c r="AU18" s="149">
+        <v>0</v>
+      </c>
+      <c r="AV18" s="149">
+        <v>0</v>
+      </c>
+      <c r="AW18" s="149">
+        <v>0</v>
+      </c>
+      <c r="AX18" s="149">
+        <v>0</v>
+      </c>
+      <c r="AY18" s="149">
+        <v>0</v>
+      </c>
+      <c r="AZ18" s="149">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>187</v>
       </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>0</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19">
-        <v>0</v>
-      </c>
-      <c r="V19">
-        <v>0</v>
-      </c>
-      <c r="W19">
-        <v>0</v>
-      </c>
-      <c r="X19">
-        <v>0</v>
-      </c>
-      <c r="Y19">
-        <v>0</v>
-      </c>
-      <c r="Z19">
-        <v>0</v>
-      </c>
-      <c r="AA19">
-        <v>0</v>
-      </c>
-      <c r="AB19">
-        <v>0</v>
-      </c>
-      <c r="AC19">
-        <v>0</v>
-      </c>
-      <c r="AD19">
-        <v>0</v>
-      </c>
-      <c r="AE19">
-        <v>0</v>
-      </c>
-      <c r="AF19">
+      <c r="B19" s="149">
+        <v>0</v>
+      </c>
+      <c r="C19" s="149">
+        <v>0</v>
+      </c>
+      <c r="D19" s="149">
+        <v>0</v>
+      </c>
+      <c r="E19" s="149">
+        <v>0</v>
+      </c>
+      <c r="F19" s="149">
+        <v>0</v>
+      </c>
+      <c r="G19" s="149">
+        <v>0</v>
+      </c>
+      <c r="H19" s="149">
+        <v>0</v>
+      </c>
+      <c r="I19" s="149">
+        <v>0</v>
+      </c>
+      <c r="J19" s="149">
+        <v>0</v>
+      </c>
+      <c r="K19" s="149">
+        <v>0</v>
+      </c>
+      <c r="L19" s="149">
+        <v>0</v>
+      </c>
+      <c r="M19" s="149">
+        <v>0</v>
+      </c>
+      <c r="N19" s="149">
+        <v>0</v>
+      </c>
+      <c r="O19" s="149">
+        <v>0</v>
+      </c>
+      <c r="P19" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="149">
+        <v>0</v>
+      </c>
+      <c r="R19" s="149">
+        <v>0</v>
+      </c>
+      <c r="S19" s="149">
+        <v>0</v>
+      </c>
+      <c r="T19" s="149">
+        <v>0</v>
+      </c>
+      <c r="U19" s="149">
+        <v>0</v>
+      </c>
+      <c r="V19" s="149">
+        <v>0</v>
+      </c>
+      <c r="W19" s="149">
+        <v>0</v>
+      </c>
+      <c r="X19" s="149">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="149">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="149">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="149">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="149">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="149">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="149">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="149">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="149">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="149">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="149">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="149">
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="149">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="149">
+        <v>0</v>
+      </c>
+      <c r="AL19" s="149">
+        <v>0</v>
+      </c>
+      <c r="AM19" s="149">
+        <v>0</v>
+      </c>
+      <c r="AN19" s="149">
+        <v>0</v>
+      </c>
+      <c r="AO19" s="149">
+        <v>0</v>
+      </c>
+      <c r="AP19" s="149">
+        <v>0</v>
+      </c>
+      <c r="AQ19" s="149">
+        <v>0</v>
+      </c>
+      <c r="AR19" s="149">
+        <v>0</v>
+      </c>
+      <c r="AS19" s="149">
+        <v>0</v>
+      </c>
+      <c r="AT19" s="149">
+        <v>0</v>
+      </c>
+      <c r="AU19" s="149">
+        <v>0</v>
+      </c>
+      <c r="AV19" s="149">
+        <v>0</v>
+      </c>
+      <c r="AW19" s="149">
+        <v>0</v>
+      </c>
+      <c r="AX19" s="149">
+        <v>0</v>
+      </c>
+      <c r="AY19" s="149">
+        <v>0</v>
+      </c>
+      <c r="AZ19" s="149">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>188</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="Y20">
-        <v>0</v>
-      </c>
-      <c r="Z20">
-        <v>0</v>
-      </c>
-      <c r="AA20">
-        <v>0</v>
-      </c>
-      <c r="AB20">
-        <v>0</v>
-      </c>
-      <c r="AC20">
-        <v>0</v>
-      </c>
-      <c r="AD20">
-        <v>0</v>
-      </c>
-      <c r="AE20">
-        <v>0</v>
-      </c>
-      <c r="AF20">
+      <c r="B20" s="149">
+        <v>0</v>
+      </c>
+      <c r="C20" s="149">
+        <v>0</v>
+      </c>
+      <c r="D20" s="149">
+        <v>0</v>
+      </c>
+      <c r="E20" s="149">
+        <v>0</v>
+      </c>
+      <c r="F20" s="149">
+        <v>0</v>
+      </c>
+      <c r="G20" s="149">
+        <v>0</v>
+      </c>
+      <c r="H20" s="149">
+        <v>0</v>
+      </c>
+      <c r="I20" s="149">
+        <v>0</v>
+      </c>
+      <c r="J20" s="149">
+        <v>0</v>
+      </c>
+      <c r="K20" s="149">
+        <v>0</v>
+      </c>
+      <c r="L20" s="149">
+        <v>0</v>
+      </c>
+      <c r="M20" s="149">
+        <v>0</v>
+      </c>
+      <c r="N20" s="149">
+        <v>0</v>
+      </c>
+      <c r="O20" s="149">
+        <v>0</v>
+      </c>
+      <c r="P20" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="149">
+        <v>0</v>
+      </c>
+      <c r="R20" s="149">
+        <v>0</v>
+      </c>
+      <c r="S20" s="149">
+        <v>0</v>
+      </c>
+      <c r="T20" s="149">
+        <v>0</v>
+      </c>
+      <c r="U20" s="149">
+        <v>0</v>
+      </c>
+      <c r="V20" s="149">
+        <v>0</v>
+      </c>
+      <c r="W20" s="149">
+        <v>0</v>
+      </c>
+      <c r="X20" s="149">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="149">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="149">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="149">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="149">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="149">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="149">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="149">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="149">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="149">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="149">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="149">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="149">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="149">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="149">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="149">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="149">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="149">
+        <v>0</v>
+      </c>
+      <c r="AP20" s="149">
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="149">
+        <v>0</v>
+      </c>
+      <c r="AR20" s="149">
+        <v>0</v>
+      </c>
+      <c r="AS20" s="149">
+        <v>0</v>
+      </c>
+      <c r="AT20" s="149">
+        <v>0</v>
+      </c>
+      <c r="AU20" s="149">
+        <v>0</v>
+      </c>
+      <c r="AV20" s="149">
+        <v>0</v>
+      </c>
+      <c r="AW20" s="149">
+        <v>0</v>
+      </c>
+      <c r="AX20" s="149">
+        <v>0</v>
+      </c>
+      <c r="AY20" s="149">
+        <v>0</v>
+      </c>
+      <c r="AZ20" s="149">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>189</v>
       </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
-      <c r="AB21">
-        <v>0</v>
-      </c>
-      <c r="AC21">
-        <v>0</v>
-      </c>
-      <c r="AD21">
-        <v>0</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
+      <c r="B21" s="149">
+        <v>0</v>
+      </c>
+      <c r="C21" s="149">
+        <v>0</v>
+      </c>
+      <c r="D21" s="149">
+        <v>0</v>
+      </c>
+      <c r="E21" s="149">
+        <v>0</v>
+      </c>
+      <c r="F21" s="149">
+        <v>0</v>
+      </c>
+      <c r="G21" s="149">
+        <v>0</v>
+      </c>
+      <c r="H21" s="149">
+        <v>0</v>
+      </c>
+      <c r="I21" s="149">
+        <v>0</v>
+      </c>
+      <c r="J21" s="149">
+        <v>0</v>
+      </c>
+      <c r="K21" s="149">
+        <v>0</v>
+      </c>
+      <c r="L21" s="149">
+        <v>0</v>
+      </c>
+      <c r="M21" s="149">
+        <v>0</v>
+      </c>
+      <c r="N21" s="149">
+        <v>0</v>
+      </c>
+      <c r="O21" s="149">
+        <v>0</v>
+      </c>
+      <c r="P21" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="149">
+        <v>0</v>
+      </c>
+      <c r="R21" s="149">
+        <v>0</v>
+      </c>
+      <c r="S21" s="149">
+        <v>0</v>
+      </c>
+      <c r="T21" s="149">
+        <v>0</v>
+      </c>
+      <c r="U21" s="149">
+        <v>0</v>
+      </c>
+      <c r="V21" s="149">
+        <v>0</v>
+      </c>
+      <c r="W21" s="149">
+        <v>0</v>
+      </c>
+      <c r="X21" s="149">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="149">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="149">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="149">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="149">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="149">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="149">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="149">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="149">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="149">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="149">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="149">
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="149">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="149">
+        <v>0</v>
+      </c>
+      <c r="AL21" s="149">
+        <v>0</v>
+      </c>
+      <c r="AM21" s="149">
+        <v>0</v>
+      </c>
+      <c r="AN21" s="149">
+        <v>0</v>
+      </c>
+      <c r="AO21" s="149">
+        <v>0</v>
+      </c>
+      <c r="AP21" s="149">
+        <v>0</v>
+      </c>
+      <c r="AQ21" s="149">
+        <v>0</v>
+      </c>
+      <c r="AR21" s="149">
+        <v>0</v>
+      </c>
+      <c r="AS21" s="149">
+        <v>0</v>
+      </c>
+      <c r="AT21" s="149">
+        <v>0</v>
+      </c>
+      <c r="AU21" s="149">
+        <v>0</v>
+      </c>
+      <c r="AV21" s="149">
+        <v>0</v>
+      </c>
+      <c r="AW21" s="149">
+        <v>0</v>
+      </c>
+      <c r="AX21" s="149">
+        <v>0</v>
+      </c>
+      <c r="AY21" s="149">
+        <v>0</v>
+      </c>
+      <c r="AZ21" s="149">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>190</v>
       </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>0</v>
-      </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-      <c r="X22">
-        <v>0</v>
-      </c>
-      <c r="Y22">
-        <v>0</v>
-      </c>
-      <c r="Z22">
-        <v>0</v>
-      </c>
-      <c r="AA22">
-        <v>0</v>
-      </c>
-      <c r="AB22">
-        <v>0</v>
-      </c>
-      <c r="AC22">
-        <v>0</v>
-      </c>
-      <c r="AD22">
-        <v>0</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
-      <c r="AF22">
+      <c r="B22" s="149">
+        <v>0</v>
+      </c>
+      <c r="C22" s="149">
+        <v>0</v>
+      </c>
+      <c r="D22" s="149">
+        <v>0</v>
+      </c>
+      <c r="E22" s="149">
+        <v>0</v>
+      </c>
+      <c r="F22" s="149">
+        <v>0</v>
+      </c>
+      <c r="G22" s="149">
+        <v>0</v>
+      </c>
+      <c r="H22" s="149">
+        <v>0</v>
+      </c>
+      <c r="I22" s="149">
+        <v>0</v>
+      </c>
+      <c r="J22" s="149">
+        <v>0</v>
+      </c>
+      <c r="K22" s="149">
+        <v>0</v>
+      </c>
+      <c r="L22" s="149">
+        <v>0</v>
+      </c>
+      <c r="M22" s="149">
+        <v>0</v>
+      </c>
+      <c r="N22" s="149">
+        <v>0</v>
+      </c>
+      <c r="O22" s="149">
+        <v>0</v>
+      </c>
+      <c r="P22" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="149">
+        <v>0</v>
+      </c>
+      <c r="R22" s="149">
+        <v>0</v>
+      </c>
+      <c r="S22" s="149">
+        <v>0</v>
+      </c>
+      <c r="T22" s="149">
+        <v>0</v>
+      </c>
+      <c r="U22" s="149">
+        <v>0</v>
+      </c>
+      <c r="V22" s="149">
+        <v>0</v>
+      </c>
+      <c r="W22" s="149">
+        <v>0</v>
+      </c>
+      <c r="X22" s="149">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="149">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="149">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="149">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="149">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="149">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="149">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="149">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="149">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="149">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="149">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="149">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="149">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="149">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="149">
+        <v>0</v>
+      </c>
+      <c r="AM22" s="149">
+        <v>0</v>
+      </c>
+      <c r="AN22" s="149">
+        <v>0</v>
+      </c>
+      <c r="AO22" s="149">
+        <v>0</v>
+      </c>
+      <c r="AP22" s="149">
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="149">
+        <v>0</v>
+      </c>
+      <c r="AR22" s="149">
+        <v>0</v>
+      </c>
+      <c r="AS22" s="149">
+        <v>0</v>
+      </c>
+      <c r="AT22" s="149">
+        <v>0</v>
+      </c>
+      <c r="AU22" s="149">
+        <v>0</v>
+      </c>
+      <c r="AV22" s="149">
+        <v>0</v>
+      </c>
+      <c r="AW22" s="149">
+        <v>0</v>
+      </c>
+      <c r="AX22" s="149">
+        <v>0</v>
+      </c>
+      <c r="AY22" s="149">
+        <v>0</v>
+      </c>
+      <c r="AZ22" s="149">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A23" s="47" t="s">
         <v>191</v>
       </c>
-      <c r="B23" s="47">
-        <v>0</v>
-      </c>
-      <c r="C23" s="47">
-        <v>0</v>
-      </c>
-      <c r="D23" s="47">
-        <v>0</v>
-      </c>
-      <c r="E23" s="47">
-        <v>0</v>
-      </c>
-      <c r="F23" s="47">
-        <v>0</v>
-      </c>
-      <c r="G23" s="47">
-        <v>0</v>
-      </c>
-      <c r="H23" s="47">
-        <v>0</v>
-      </c>
-      <c r="I23" s="47">
-        <v>0</v>
-      </c>
-      <c r="J23" s="47">
-        <v>0</v>
-      </c>
-      <c r="K23" s="47">
-        <v>0</v>
-      </c>
-      <c r="L23" s="47">
-        <v>0</v>
-      </c>
-      <c r="M23" s="47">
-        <v>0</v>
-      </c>
-      <c r="N23" s="47">
-        <v>0</v>
-      </c>
-      <c r="O23" s="47">
-        <v>0</v>
-      </c>
-      <c r="P23" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="47">
-        <v>0</v>
-      </c>
-      <c r="R23" s="47">
-        <v>0</v>
-      </c>
-      <c r="S23" s="47">
-        <v>0</v>
-      </c>
-      <c r="T23" s="47">
-        <v>0</v>
-      </c>
-      <c r="U23" s="47">
-        <v>0</v>
-      </c>
-      <c r="V23" s="47">
-        <v>0</v>
-      </c>
-      <c r="W23" s="47">
-        <v>0</v>
-      </c>
-      <c r="X23" s="47">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="47">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="47">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="47">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="47">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="47">
-        <v>0</v>
-      </c>
-      <c r="AD23" s="47">
-        <v>0</v>
-      </c>
-      <c r="AE23" s="47">
-        <v>0</v>
-      </c>
-      <c r="AF23" s="47">
+      <c r="B23" s="149">
+        <v>0</v>
+      </c>
+      <c r="C23" s="149">
+        <v>0</v>
+      </c>
+      <c r="D23" s="149">
+        <v>0</v>
+      </c>
+      <c r="E23" s="149">
+        <v>0</v>
+      </c>
+      <c r="F23" s="149">
+        <v>0</v>
+      </c>
+      <c r="G23" s="149">
+        <v>0</v>
+      </c>
+      <c r="H23" s="149">
+        <v>0</v>
+      </c>
+      <c r="I23" s="149">
+        <v>0</v>
+      </c>
+      <c r="J23" s="149">
+        <v>0</v>
+      </c>
+      <c r="K23" s="149">
+        <v>0</v>
+      </c>
+      <c r="L23" s="149">
+        <v>0</v>
+      </c>
+      <c r="M23" s="149">
+        <v>0</v>
+      </c>
+      <c r="N23" s="149">
+        <v>0</v>
+      </c>
+      <c r="O23" s="149">
+        <v>0</v>
+      </c>
+      <c r="P23" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="149">
+        <v>0</v>
+      </c>
+      <c r="R23" s="149">
+        <v>0</v>
+      </c>
+      <c r="S23" s="149">
+        <v>0</v>
+      </c>
+      <c r="T23" s="149">
+        <v>0</v>
+      </c>
+      <c r="U23" s="149">
+        <v>0</v>
+      </c>
+      <c r="V23" s="149">
+        <v>0</v>
+      </c>
+      <c r="W23" s="149">
+        <v>0</v>
+      </c>
+      <c r="X23" s="149">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="149">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="149">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="149">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="149">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="149">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="149">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="149">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="149">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="149">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="149">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="149">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="149">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="149">
+        <v>0</v>
+      </c>
+      <c r="AL23" s="149">
+        <v>0</v>
+      </c>
+      <c r="AM23" s="149">
+        <v>0</v>
+      </c>
+      <c r="AN23" s="149">
+        <v>0</v>
+      </c>
+      <c r="AO23" s="149">
+        <v>0</v>
+      </c>
+      <c r="AP23" s="149">
+        <v>0</v>
+      </c>
+      <c r="AQ23" s="149">
+        <v>0</v>
+      </c>
+      <c r="AR23" s="149">
+        <v>0</v>
+      </c>
+      <c r="AS23" s="149">
+        <v>0</v>
+      </c>
+      <c r="AT23" s="149">
+        <v>0</v>
+      </c>
+      <c r="AU23" s="149">
+        <v>0</v>
+      </c>
+      <c r="AV23" s="149">
+        <v>0</v>
+      </c>
+      <c r="AW23" s="149">
+        <v>0</v>
+      </c>
+      <c r="AX23" s="149">
+        <v>0</v>
+      </c>
+      <c r="AY23" s="149">
+        <v>0</v>
+      </c>
+      <c r="AZ23" s="149">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A24" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="B24" s="47">
-        <v>0</v>
-      </c>
-      <c r="C24" s="47">
-        <v>0</v>
-      </c>
-      <c r="D24" s="47">
-        <v>0</v>
-      </c>
-      <c r="E24" s="47">
-        <v>0</v>
-      </c>
-      <c r="F24" s="47">
-        <v>0</v>
-      </c>
-      <c r="G24" s="47">
-        <v>0</v>
-      </c>
-      <c r="H24" s="47">
-        <v>0</v>
-      </c>
-      <c r="I24" s="47">
-        <v>0</v>
-      </c>
-      <c r="J24" s="47">
-        <v>0</v>
-      </c>
-      <c r="K24" s="47">
-        <v>0</v>
-      </c>
-      <c r="L24" s="47">
-        <v>0</v>
-      </c>
-      <c r="M24" s="47">
-        <v>0</v>
-      </c>
-      <c r="N24" s="47">
-        <v>0</v>
-      </c>
-      <c r="O24" s="47">
-        <v>0</v>
-      </c>
-      <c r="P24" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="47">
-        <v>0</v>
-      </c>
-      <c r="R24" s="47">
-        <v>0</v>
-      </c>
-      <c r="S24" s="47">
-        <v>0</v>
-      </c>
-      <c r="T24" s="47">
-        <v>0</v>
-      </c>
-      <c r="U24" s="47">
-        <v>0</v>
-      </c>
-      <c r="V24" s="47">
-        <v>0</v>
-      </c>
-      <c r="W24" s="47">
-        <v>0</v>
-      </c>
-      <c r="X24" s="47">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="47">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="47">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="47">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="47">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="47">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="47">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="47">
-        <v>0</v>
-      </c>
-      <c r="AF24" s="47">
+      <c r="B24" s="149">
+        <v>0</v>
+      </c>
+      <c r="C24" s="149">
+        <v>0</v>
+      </c>
+      <c r="D24" s="149">
+        <v>0</v>
+      </c>
+      <c r="E24" s="149">
+        <v>0</v>
+      </c>
+      <c r="F24" s="149">
+        <v>0</v>
+      </c>
+      <c r="G24" s="149">
+        <v>0</v>
+      </c>
+      <c r="H24" s="149">
+        <v>0</v>
+      </c>
+      <c r="I24" s="149">
+        <v>0</v>
+      </c>
+      <c r="J24" s="149">
+        <v>0</v>
+      </c>
+      <c r="K24" s="149">
+        <v>0</v>
+      </c>
+      <c r="L24" s="149">
+        <v>0</v>
+      </c>
+      <c r="M24" s="149">
+        <v>0</v>
+      </c>
+      <c r="N24" s="149">
+        <v>0</v>
+      </c>
+      <c r="O24" s="149">
+        <v>0</v>
+      </c>
+      <c r="P24" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="149">
+        <v>0</v>
+      </c>
+      <c r="R24" s="149">
+        <v>0</v>
+      </c>
+      <c r="S24" s="149">
+        <v>0</v>
+      </c>
+      <c r="T24" s="149">
+        <v>0</v>
+      </c>
+      <c r="U24" s="149">
+        <v>0</v>
+      </c>
+      <c r="V24" s="149">
+        <v>0</v>
+      </c>
+      <c r="W24" s="149">
+        <v>0</v>
+      </c>
+      <c r="X24" s="149">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="149">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="149">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="149">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="149">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="149">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="149">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="149">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="149">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="149">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="149">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="149">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="149">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="149">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="149">
+        <v>0</v>
+      </c>
+      <c r="AM24" s="149">
+        <v>0</v>
+      </c>
+      <c r="AN24" s="149">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="149">
+        <v>0</v>
+      </c>
+      <c r="AP24" s="149">
+        <v>0</v>
+      </c>
+      <c r="AQ24" s="149">
+        <v>0</v>
+      </c>
+      <c r="AR24" s="149">
+        <v>0</v>
+      </c>
+      <c r="AS24" s="149">
+        <v>0</v>
+      </c>
+      <c r="AT24" s="149">
+        <v>0</v>
+      </c>
+      <c r="AU24" s="149">
+        <v>0</v>
+      </c>
+      <c r="AV24" s="149">
+        <v>0</v>
+      </c>
+      <c r="AW24" s="149">
+        <v>0</v>
+      </c>
+      <c r="AX24" s="149">
+        <v>0</v>
+      </c>
+      <c r="AY24" s="149">
+        <v>0</v>
+      </c>
+      <c r="AZ24" s="149">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A25" s="48" t="s">
         <v>193</v>
       </c>
-      <c r="B25" s="47">
-        <v>0</v>
-      </c>
-      <c r="C25" s="47">
-        <v>0</v>
-      </c>
-      <c r="D25" s="47">
-        <v>0</v>
-      </c>
-      <c r="E25" s="47">
-        <v>0</v>
-      </c>
-      <c r="F25" s="47">
-        <v>0</v>
-      </c>
-      <c r="G25" s="47">
-        <v>0</v>
-      </c>
-      <c r="H25" s="47">
-        <v>0</v>
-      </c>
-      <c r="I25" s="47">
-        <v>0</v>
-      </c>
-      <c r="J25" s="47">
-        <v>0</v>
-      </c>
-      <c r="K25" s="47">
-        <v>0</v>
-      </c>
-      <c r="L25" s="47">
-        <v>0</v>
-      </c>
-      <c r="M25" s="47">
-        <v>0</v>
-      </c>
-      <c r="N25" s="47">
-        <v>0</v>
-      </c>
-      <c r="O25" s="47">
-        <v>0</v>
-      </c>
-      <c r="P25" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="47">
-        <v>0</v>
-      </c>
-      <c r="R25" s="47">
-        <v>0</v>
-      </c>
-      <c r="S25" s="47">
-        <v>0</v>
-      </c>
-      <c r="T25" s="47">
-        <v>0</v>
-      </c>
-      <c r="U25" s="47">
-        <v>0</v>
-      </c>
-      <c r="V25" s="47">
-        <v>0</v>
-      </c>
-      <c r="W25" s="47">
-        <v>0</v>
-      </c>
-      <c r="X25" s="47">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="47">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="47">
-        <v>0</v>
-      </c>
-      <c r="AA25" s="47">
-        <v>0</v>
-      </c>
-      <c r="AB25" s="47">
-        <v>0</v>
-      </c>
-      <c r="AC25" s="47">
-        <v>0</v>
-      </c>
-      <c r="AD25" s="47">
-        <v>0</v>
-      </c>
-      <c r="AE25" s="47">
-        <v>0</v>
-      </c>
-      <c r="AF25" s="47">
+      <c r="B25" s="149">
+        <v>0</v>
+      </c>
+      <c r="C25" s="149">
+        <v>0</v>
+      </c>
+      <c r="D25" s="149">
+        <v>0</v>
+      </c>
+      <c r="E25" s="149">
+        <v>0</v>
+      </c>
+      <c r="F25" s="149">
+        <v>0</v>
+      </c>
+      <c r="G25" s="149">
+        <v>0</v>
+      </c>
+      <c r="H25" s="149">
+        <v>0</v>
+      </c>
+      <c r="I25" s="149">
+        <v>0</v>
+      </c>
+      <c r="J25" s="149">
+        <v>0</v>
+      </c>
+      <c r="K25" s="149">
+        <v>0</v>
+      </c>
+      <c r="L25" s="149">
+        <v>0</v>
+      </c>
+      <c r="M25" s="149">
+        <v>0</v>
+      </c>
+      <c r="N25" s="149">
+        <v>0</v>
+      </c>
+      <c r="O25" s="149">
+        <v>0</v>
+      </c>
+      <c r="P25" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="149">
+        <v>0</v>
+      </c>
+      <c r="R25" s="149">
+        <v>0</v>
+      </c>
+      <c r="S25" s="149">
+        <v>0</v>
+      </c>
+      <c r="T25" s="149">
+        <v>0</v>
+      </c>
+      <c r="U25" s="149">
+        <v>0</v>
+      </c>
+      <c r="V25" s="149">
+        <v>0</v>
+      </c>
+      <c r="W25" s="149">
+        <v>0</v>
+      </c>
+      <c r="X25" s="149">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="149">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="149">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="149">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="149">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="149">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="149">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="149">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="149">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="149">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="149">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="149">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="149">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="149">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="149">
+        <v>0</v>
+      </c>
+      <c r="AM25" s="149">
+        <v>0</v>
+      </c>
+      <c r="AN25" s="149">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="149">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="149">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="149">
+        <v>0</v>
+      </c>
+      <c r="AR25" s="149">
+        <v>0</v>
+      </c>
+      <c r="AS25" s="149">
+        <v>0</v>
+      </c>
+      <c r="AT25" s="149">
+        <v>0</v>
+      </c>
+      <c r="AU25" s="149">
+        <v>0</v>
+      </c>
+      <c r="AV25" s="149">
+        <v>0</v>
+      </c>
+      <c r="AW25" s="149">
+        <v>0</v>
+      </c>
+      <c r="AX25" s="149">
+        <v>0</v>
+      </c>
+      <c r="AY25" s="149">
+        <v>0</v>
+      </c>
+      <c r="AZ25" s="149">
         <v>0</v>
       </c>
     </row>
